--- a/forms/app/vineland.xlsx
+++ b/forms/app/vineland.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L266"/>
+  <dimension ref="A1:L259"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,6 +496,8 @@
           <t>Participant</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>field-list</t>
@@ -506,6 +508,11 @@
           <t>./source = 'user'</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -518,6 +525,16 @@
           <t>source</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -530,6 +547,16 @@
           <t>source_id</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,11 +574,19 @@
           <t>User</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
           <t>field-list</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -564,6 +599,16 @@
           <t>contact_id</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -576,6 +621,16 @@
           <t>name</t>
         </is>
       </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -583,55 +638,66 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>contact</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Select child / beneficiary</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>db:person</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>_id</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Select participant</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>select-contact type-participant</t>
-        </is>
-      </c>
+          <t>patient_uuid</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>../inputs/contact/_id</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -639,347 +705,576 @@
           <t>patient_id</t>
         </is>
       </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>../inputs/contact/patient_id</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>name</t>
-        </is>
-      </c>
+          <t>patient_name</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>../inputs/contact/name</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>age</t>
-        </is>
-      </c>
+          <t>screened_by</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>../inputs/user/contact_id</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hidden</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>reported_date</t>
-        </is>
-      </c>
+          <t>screened_by_name</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>../inputs/user/name</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>g_intro</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Vineland-style Social Maturity Scale (VSMS)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>vineland_disclaimer</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>This assessment is a social maturity screening tool. It does not provide a diagnosis. Results must be interpreted by a qualified clinician.</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one yesno</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>patient_uuid</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>../inputs/contact/_id</t>
-        </is>
-      </c>
+          <t>acknowledged</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>I confirm that this assessment is being completed by or reviewed with a trained/authorized health worker.</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>. = 'yes'</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>You must confirm before continuing.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>patient_id</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>../inputs/contact/patient_id</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>patient_name</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>../inputs/contact/name</t>
-        </is>
-      </c>
+          <t>g_child</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Child details &amp; assessment date</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>screened_by</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>../inputs/user/contact_id</t>
-        </is>
-      </c>
+          <t>assessment_date</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Assessment date</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>today()</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>screened_by_name</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>../inputs/user/name</t>
-        </is>
-      </c>
+          <t>child_dob</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Child date of birth</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Contacts do not store date of birth, so it is captured here.</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>. &lt;= today() and today() - . &lt;= 5479</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Date of birth must be today or earlier, and the child must be 15 years or younger.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>g_intro</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Vineland-style Social Maturity Scale (VSMS)</t>
-        </is>
-      </c>
+          <t>ca_days</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>int(${assessment_date} - ${child_dob})</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>vineland_disclaimer</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>This assessment is a social maturity screening tool. It does not provide a diagnosis. Results must be interpreted by a qualified clinician.</t>
-        </is>
-      </c>
+          <t>ca_months_dec</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>${ca_days} div 30.4375</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one yesno</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>acknowledged</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>I confirm that this assessment is being completed by or reviewed with a trained/authorized health worker.</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>. = 'yes'</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>You must confirm before continuing.</t>
-        </is>
-      </c>
+          <t>ca_months_floor</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>floor(${ca_months_dec})</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>ca_years_display</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>floor(${ca_days} div 365.25)</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>g_child</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Child details &amp; assessment date</t>
-        </is>
-      </c>
+          <t>ca_rem_months</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>floor((${ca_days} mod 365) div 30.4375)</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>assessment_date</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Assessment date</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>today()</t>
-        </is>
-      </c>
+          <t>age_valid</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>if(${ca_days} &gt;= 0 and ${ca_months_dec} &lt;= 180 and ${acknowledged} = 'yes', 'yes', 'no')</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>child_dob</t>
+          <t>dob_warning</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Child date of birth</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Contacts do not store date of birth, so it is captured here.</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>. &lt;= today() and today() - . &lt;= 5479</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Date of birth must be today or earlier, and the child must be 15 years or younger.</t>
-        </is>
-      </c>
+          <t>**WARNING:** Child date of birth is missing or invalid. Please enter DOB before scoring. Do not guess age.</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>${child_dob} = '' or ${age_valid} != 'yes'</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ca_days</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>int(${assessment_date} - ${child_dob})</t>
-        </is>
-      </c>
+          <t>ca_display</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Chronological age: **${ca_years_display}y ${ca_rem_months}m** (${ca_days} days).</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>${age_valid} = 'yes'</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one yesno</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ca_months_dec</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>${ca_days} div 30.4375</t>
-        </is>
-      </c>
+          <t>show_all</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Show all VSMS items? (trained assessors)</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>No = show birth through child age band; future bands hidden. Yes = show all bands.</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ca_months_floor</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>floor(${ca_months_dec})</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -989,165 +1284,267 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ca_years_display</t>
-        </is>
-      </c>
+          <t>ca_band</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>floor(${ca_days} div 365.25)</t>
-        </is>
-      </c>
+          <t>if(${ca_months_dec} &lt; 12, 1, if(${ca_months_dec} &lt; 24, 2, if(${ca_months_dec} &lt; 36, 3, if(${ca_months_dec} &lt; 48, 4, if(${ca_months_dec} &lt; 60, 5, if(${ca_months_dec} &lt; 72, 6, if(${ca_months_dec} &lt; 84, 7, if(${ca_months_dec} &lt; 96, 8, if(${ca_months_dec} &lt; 108, 9, if(${ca_months_dec} &lt; 120, 10, if(${ca_months_dec} &lt; 132, 11, if(${ca_months_dec} &lt; 144, 12, 13))))))))))))</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ca_rem_months</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>floor((${ca_days} mod 365) div 30.4375)</t>
-        </is>
-      </c>
+          <t>g_y0_1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0–1 Years</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 1</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>age_valid</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>if(${ca_days} &gt;= 0 and ${ca_months_dec} &lt;= 180 and ${acknowledged} = 'yes', 'yes', 'no')</t>
-        </is>
-      </c>
+          <t>item_1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1. Cries, laughs</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dob_warning</t>
+          <t>item_2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>**WARNING:** Child date of birth is missing or invalid. Please enter DOB before scoring. Do not guess age.</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>${child_dob} = '' or ${age_valid} != 'yes'</t>
-        </is>
-      </c>
+          <t>2. Balances head</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ca_display</t>
+          <t>item_3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Chronological age: **${ca_years_display}y ${ca_rem_months}m** (${ca_days} days).</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>${age_valid} = 'yes'</t>
-        </is>
-      </c>
+          <t>3. Grasps object within reach</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one yesno</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>show_all</t>
+          <t>item_4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Show all VSMS items? (trained assessors)</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>No = show birth through child age band; future bands hidden. Yes = show all bands.</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+          <t>4. Reaches for familiar persons</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>item_5</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>5. Rolls over (unassisted)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ca_band</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>if(${ca_months_dec} &lt; 12, 1, if(${ca_months_dec} &lt; 24, 2, if(${ca_months_dec} &lt; 36, 3, if(${ca_months_dec} &lt; 48, 4, if(${ca_months_dec} &lt; 60, 5, if(${ca_months_dec} &lt; 72, 6, if(${ca_months_dec} &lt; 84, 7, if(${ca_months_dec} &lt; 96, 8, if(${ca_months_dec} &lt; 108, 9, if(${ca_months_dec} &lt; 120, 10, if(${ca_months_dec} &lt; 132, 11, if(${ca_months_dec} &lt; 144, 12, 13))))))))))))</t>
-        </is>
-      </c>
+          <t>item_6</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>6. Reaches for nearby objects</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>g_y0_1</t>
+          <t>item_7</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0–1 Years</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 1</t>
-        </is>
-      </c>
+          <t>7. Occupies self unattended*</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1157,19 +1554,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>item_1</t>
+          <t>item_8</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1. Cries, laughs</t>
-        </is>
-      </c>
+          <t>8. Sits unsupported</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1179,19 +1584,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>item_2</t>
+          <t>item_9</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>2. Balances head</t>
-        </is>
-      </c>
+          <t>9. Pulls self upright</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1201,19 +1614,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>item_3</t>
+          <t>item_10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3. Grasps object within reach</t>
-        </is>
-      </c>
+          <t>10. Talks, imitates sounds</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1223,19 +1644,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>item_4</t>
+          <t>item_11</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>4. Reaches for familiar persons</t>
-        </is>
-      </c>
+          <t>11. Drinks from cup or glass assisted</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1245,19 +1674,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>item_5</t>
+          <t>item_12</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>5. Rolls over (unassisted)</t>
-        </is>
-      </c>
+          <t>12. Moves about on floor, (creeping, crawling)</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1267,19 +1704,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>item_6</t>
+          <t>item_13</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>6. Reaches for nearby objects</t>
-        </is>
-      </c>
+          <t>13. Grasps with thumb and finger</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1289,24 +1734,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>item_7</t>
+          <t>item_14</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>7. Occupies self unattended*</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>14. Demands personal attention</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1316,19 +1764,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>item_8</t>
+          <t>item_15</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8. Sits unsupported</t>
-        </is>
-      </c>
+          <t>15. Stands alone</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1338,19 +1794,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>item_9</t>
+          <t>item_16</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>9. Pulls self upright</t>
-        </is>
-      </c>
+          <t>16. Does not drool</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1360,63 +1824,75 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>item_10</t>
+          <t>item_17</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>10. Talks, imitates sounds</t>
-        </is>
-      </c>
+          <t>17. Follows simple instructions</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>item_11</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>11. Drinks from cup or glass assisted</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>item_12</t>
+          <t>g_y1_2</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>12. Moves about on floor, (creeping, crawling)</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>1–2 Years</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 2</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1426,19 +1902,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>item_13</t>
+          <t>item_18</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>13. Grasps with thumb and finger</t>
-        </is>
-      </c>
+          <t>18. Walks about room unattended</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1448,19 +1932,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>item_14</t>
+          <t>item_19</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>14. Demands personal attention</t>
-        </is>
-      </c>
+          <t>19. Marks with pencil or crayon</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1470,19 +1962,27 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>item_15</t>
+          <t>item_20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>15. Stands alone</t>
-        </is>
-      </c>
+          <t>20. Masticates (chews) solid or semi-solid food</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1492,19 +1992,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>item_16</t>
+          <t>item_21</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>16. Does not drool</t>
-        </is>
-      </c>
+          <t>21. Removes shoes or sandals, pulls off socks</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1514,48 +2022,91 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>item_17</t>
+          <t>item_22</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>17. Follows simple instructions</t>
-        </is>
-      </c>
+          <t>22. Transfers objects</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>item_23</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>23. Overcomes simple obstacles*</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>g_y1_2</t>
+          <t>item_24</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>1–2 Years</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 2</t>
-        </is>
-      </c>
+          <t>24. Fetches or carries familiar objects</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1565,19 +2116,27 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>item_18</t>
+          <t>item_25</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>18. Walks about room unattended</t>
-        </is>
-      </c>
+          <t>25. Drinks from cup or glass unassisted</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1587,12 +2146,17 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>item_19</t>
+          <t>item_26</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>19. Marks with pencil or crayon</t>
+          <t>26. Walks or uses a go-cart for walking*</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -1600,6 +2164,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1609,19 +2180,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>item_20</t>
+          <t>item_27</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>20. Masticates (chews) solid or semi-solid food</t>
-        </is>
-      </c>
+          <t>27. Plays with own hands</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1631,19 +2210,27 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>item_21</t>
+          <t>item_28</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>21. Removes shoes or sandals, pulls off socks</t>
-        </is>
-      </c>
+          <t>28. Eats with own hands</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr"/>
       <c r="E63" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1653,19 +2240,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>item_22</t>
+          <t>item_29</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>22. Transfers objects</t>
-        </is>
-      </c>
+          <t>29. Goes about house or yard</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1675,24 +2270,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>item_23</t>
+          <t>item_30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>23. Overcomes simple obstacles*</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>30. Discriminates edible substances from non-edibles</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1702,19 +2300,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>item_24</t>
+          <t>item_31</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>24. Fetches or carries familiar objects</t>
-        </is>
-      </c>
+          <t>31. Uses names of familiar objects</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1724,19 +2330,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>item_25</t>
+          <t>item_32</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>25. Drinks from cup or glass unassisted</t>
-        </is>
-      </c>
+          <t>32. Walks up-stairs unassisted</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1746,24 +2360,27 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>item_26</t>
+          <t>item_33</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>26. Walks or uses a go-cart for walking*</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>33. Unwraps sweets, chocolates</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
       <c r="E68" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1773,63 +2390,75 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>item_27</t>
+          <t>item_34</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>27. Plays with own hands</t>
-        </is>
-      </c>
+          <t>34. Talks in short sentences</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
       <c r="E69" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>item_28</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>28. Eats with own hands</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr"/>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>item_29</t>
+          <t>g_y2_3</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>29. Goes about house or yard</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>2–3 Years</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 3</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1839,19 +2468,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>item_30</t>
+          <t>item_35</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>30. Discriminates edible substances from non-edibles</t>
-        </is>
-      </c>
+          <t>35. Signals (asks) to go to toilet</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
       <c r="E72" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1861,19 +2498,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>item_31</t>
+          <t>item_36</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>31. Uses names of familiar objects</t>
-        </is>
-      </c>
+          <t>36. Initiates own play activities</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
       <c r="E73" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1883,19 +2528,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>item_32</t>
+          <t>item_37</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>32. Walks up-stairs unassisted</t>
-        </is>
-      </c>
+          <t>37. Removes shirt or frock (if unbuttoned)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
       <c r="E74" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1905,19 +2558,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>item_33</t>
+          <t>item_38</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>33. Unwraps sweets, chocolates</t>
-        </is>
-      </c>
+          <t>38. Eats with spoon</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
       <c r="E75" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1927,48 +2588,87 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>item_34</t>
+          <t>item_39</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>34. Talks in short sentences</t>
-        </is>
-      </c>
+          <t>39. Drinks (water) unassisted (Gets drink unassisted)</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
       <c r="E76" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>item_40</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>40. Dries own hands</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>g_y2_3</t>
+          <t>item_41</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>2–3 Years</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 3</t>
-        </is>
-      </c>
+          <t>41. Avoids simple hazards</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1978,19 +2678,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>item_35</t>
+          <t>item_42</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>35. Signals (asks) to go to toilet</t>
-        </is>
-      </c>
+          <t>42. Puts on shirt or frock unassisted (need not button)</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
       <c r="E79" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2000,19 +2708,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>item_36</t>
+          <t>item_43</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>36. Initiates own play activities</t>
-        </is>
-      </c>
+          <t>43. Can do paper folding</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
       <c r="E80" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2022,63 +2738,75 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>item_37</t>
+          <t>item_44</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>37. Removes shirt or frock (if unbuttoned)</t>
-        </is>
-      </c>
+          <t>44. Relates experiences</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
       <c r="E81" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>item_38</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>38. Eats with spoon</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr"/>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>item_39</t>
+          <t>g_y3_4</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>39. Drinks (water) unassisted (Gets drink unassisted)</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>3–4 Years</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 4</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2088,19 +2816,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>item_40</t>
+          <t>item_45</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>40. Dries own hands</t>
-        </is>
-      </c>
+          <t>45. Walks down stairs, one step at a time</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
       <c r="E84" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2110,19 +2846,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>item_41</t>
+          <t>item_46</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>41. Avoids simple hazards</t>
-        </is>
-      </c>
+          <t>46. Plays cooperatively at kindergarten level</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2132,19 +2876,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>item_42</t>
+          <t>item_47</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>42. Puts on shirt or frock unassisted (need not button)</t>
-        </is>
-      </c>
+          <t>47. Buttons shirt or frock</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2154,19 +2906,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>item_43</t>
+          <t>item_48</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>43. Can do paper folding</t>
-        </is>
-      </c>
+          <t>48. Helps at little household tasks</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
       <c r="E87" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2176,70 +2936,105 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>item_44</t>
+          <t>item_49</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>44. Relates experiences</t>
-        </is>
-      </c>
+          <t>49. Performs for others</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>item_50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>50. Washes hands unaided</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>g_y3_4</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>3–4 Years</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 4</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>item_45</t>
+          <t>g_y4_5</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>45. Walks down stairs, one step at a time</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>4–5 Years</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 5</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2249,19 +3044,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>item_46</t>
+          <t>item_51</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>46. Plays cooperatively at kindergarten level</t>
-        </is>
-      </c>
+          <t>51. Cares for self at toilet</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
       <c r="E92" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2271,19 +3074,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>item_47</t>
+          <t>item_52</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>47. Buttons shirt or frock</t>
-        </is>
-      </c>
+          <t>52. Washes face unassisted</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
       <c r="E93" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2293,19 +3104,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>item_48</t>
+          <t>item_53</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>48. Helps at little household tasks</t>
-        </is>
-      </c>
+          <t>53. Goes about neighbourhood unattended</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2315,19 +3134,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>item_49</t>
+          <t>item_54</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>49. Performs for others</t>
-        </is>
-      </c>
+          <t>54. Dresses self except for tying or buttoning</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
       <c r="E95" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2337,70 +3164,105 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>item_50</t>
+          <t>item_55</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>50. Washes hands unaided</t>
-        </is>
-      </c>
+          <t>55. Uses pencils or crayon for drawing</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>item_56</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>56. Plays competitive exercise games</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>g_y4_5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>4–5 Years</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 5</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>item_51</t>
+          <t>g_y5_6</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>51. Cares for self at toilet</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>5–6 Years</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 6</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2410,19 +3272,27 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>item_52</t>
+          <t>item_57</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>52. Washes face unassisted</t>
-        </is>
-      </c>
+          <t>57. Uses hoops, flies kites, rides tricycles</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2432,19 +3302,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>item_53</t>
+          <t>item_58</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>53. Goes about neighbourhood unattended</t>
-        </is>
-      </c>
+          <t>58. Prints (writes) simple words</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2454,19 +3332,27 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>item_54</t>
+          <t>item_59</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>54. Dresses self except for tying or buttoning</t>
-        </is>
-      </c>
+          <t>59. Plays simple table games</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
       <c r="E102" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2476,19 +3362,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>item_55</t>
+          <t>item_60</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>55. Uses pencils or crayon for drawing</t>
-        </is>
-      </c>
+          <t>60. Is trusted with money</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr"/>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2498,19 +3392,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>item_56</t>
+          <t>item_61</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>56. Plays competitive exercise games</t>
-        </is>
-      </c>
+          <t>61. Goes to school unattended</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
       <c r="E104" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr"/>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2518,6 +3420,17 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr"/>
+      <c r="I105" t="inlineStr"/>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2527,19 +3440,27 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>g_y5_6</t>
+          <t>g_y6_7</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>5–6 Years</t>
-        </is>
-      </c>
+          <t>6–7 Years</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr">
         <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 6</t>
-        </is>
-      </c>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 7</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr"/>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2549,19 +3470,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>item_57</t>
+          <t>item_62</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>57. Uses hoops, flies kites, rides tricycles</t>
-        </is>
-      </c>
+          <t>62. Mixes rice properly unassisted</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
       <c r="E107" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr"/>
+      <c r="I107" t="inlineStr"/>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2571,19 +3500,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>item_58</t>
+          <t>item_63</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>58. Prints (writes) simple words</t>
-        </is>
-      </c>
+          <t>63. Uses pencil for writing</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2593,19 +3530,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>item_59</t>
+          <t>item_64</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>59. Plays simple table games</t>
-        </is>
-      </c>
+          <t>64. Bathes self assisted</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
       <c r="E109" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr"/>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2615,12 +3560,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>item_60</t>
+          <t>item_65</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>60. Is trusted with money</t>
+          <t>65. Goes to bed unassisted*</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -2628,57 +3578,91 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>item_61</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>61. Goes to school unattended</t>
-        </is>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr"/>
+      <c r="C111" t="inlineStr"/>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr"/>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>g_y7_8</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>7–8 Years</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 8</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>g_y6_7</t>
+          <t>item_66</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>6–7 Years</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 7</t>
-        </is>
-      </c>
+          <t>66. Tells time to quarter hour</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr"/>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2688,12 +3672,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>item_62</t>
+          <t>item_67</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>62. Mixes rice properly unassisted</t>
+          <t>67. Helps himself during meals*</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -2701,6 +3690,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2710,19 +3706,27 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>item_63</t>
+          <t>item_68</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>63. Uses pencil for writing</t>
-        </is>
-      </c>
+          <t>68. Refuses to believe in magic and fairy tales</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
       <c r="E115" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2732,12 +3736,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>item_64</t>
+          <t>item_69</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>64. Bathes self assisted</t>
+          <t>69. Participates in pre-adolescent play*</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -2745,6 +3754,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2754,24 +3770,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>item_65</t>
+          <t>item_70</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>65. Goes to bed unassisted*</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>70. Combs or brushes hair</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
       <c r="E117" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2779,6 +3798,17 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B118" t="inlineStr"/>
+      <c r="C118" t="inlineStr"/>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2788,19 +3818,27 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>g_y7_8</t>
+          <t>g_y8_9</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>7–8 Years</t>
-        </is>
-      </c>
+          <t>8–9 Years</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr">
         <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 8</t>
-        </is>
-      </c>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 9</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2810,12 +3848,17 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>item_66</t>
+          <t>item_71</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>66. Tells time to quarter hour</t>
+          <t>71. Uses tools or utensils*</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -2823,6 +3866,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2832,12 +3882,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>item_67</t>
+          <t>item_72</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>67. Helps himself during meals*</t>
+          <t>72. Does routine household tasks*</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -2850,6 +3900,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2859,19 +3916,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>item_68</t>
+          <t>item_73</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>68. Refuses to believe in magic and fairy tales</t>
-        </is>
-      </c>
+          <t>73. Reads on own initiative</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
+      <c r="I122" t="inlineStr"/>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2881,75 +3946,105 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>item_69</t>
+          <t>item_74</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>69. Participates in pre-adolescent play*</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>74. Bathes self unaided</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>item_70</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>70. Combs or brushes hair</t>
-        </is>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr"/>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>g_y9_10</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>9–10 Years</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 10</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr"/>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>g_y8_9</t>
+          <t>item_75</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>8–9 Years</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 9</t>
-        </is>
-      </c>
+          <t>75. Cares for self at table (meals)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr"/>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2959,12 +4054,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>item_71</t>
+          <t>item_76</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>71. Uses tools or utensils*</t>
+          <t>76. Makes minor purchases*</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -2977,6 +4072,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2986,97 +4088,139 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>item_72</t>
+          <t>item_77</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>72. Does routine household tasks*</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>77. Goes about home town freely</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>item_73</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>73. Reads on own initiative</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr"/>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>item_74</t>
+          <t>g_y10_11</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>74. Bathes self unaided</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>10–11 Years</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 11</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>item_78</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>78. Writes occasional short letters to friends</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr"/>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>g_y9_10</t>
+          <t>item_79</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>9–10 Years</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 10</t>
-        </is>
-      </c>
+          <t>79. Makes independent choice of shops*</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3086,12 +4230,17 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>item_75</t>
+          <t>item_80</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>75. Cares for self at table (meals)</t>
+          <t>80. Does small remunerative work; makes articles*</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -3099,6 +4248,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3108,75 +4264,105 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>item_76</t>
+          <t>item_81</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>76. Makes minor purchases*</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>81. Answers ads; writes letters for information</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>item_77</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>77. Goes about home town freely</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>begin group</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>g_y11_12</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>11–12 Years</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 12</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>g_y10_11</t>
+          <t>item_82</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>10–11 Years</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 11</t>
-        </is>
-      </c>
+          <t>82. Does simple creative work</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3186,19 +4372,27 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>item_78</t>
+          <t>item_83</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>78. Writes occasional short letters to friends</t>
-        </is>
-      </c>
+          <t>83. Is left to care for self or others</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3208,102 +4402,135 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>item_79</t>
+          <t>item_84</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>79. Makes independent choice of shops*</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
+          <t>84. Enjoys reading books, newspapers, magazines</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>item_80</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>80. Does small remunerative work; makes articles*</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>item_81</t>
+          <t>g_y12_15</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>81. Answers ads; writes letters for information</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>12–15 Years</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>${show_all} = 'yes' or ${ca_band} &gt;= 13</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr"/>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>select_one vsms_response</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>item_85</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>85. Plays difficult games</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>select_one vsms_response</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>g_y11_12</t>
+          <t>item_86</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>11–12 Years</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 12</t>
-        </is>
-      </c>
+          <t>86. Exercises complete care for dress</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3313,12 +4540,17 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>item_82</t>
+          <t>item_87</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>82. Does simple creative work</t>
+          <t>87. Buys own clothing accessories*</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -3326,6 +4558,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr"/>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
+      <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3335,12 +4574,17 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>item_83</t>
+          <t>item_88</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>83. Is left to care for self or others</t>
+          <t>88. Engages in adolescent group activities*</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>Speech/Language-related</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -3348,6 +4592,13 @@
           <t>yes</t>
         </is>
       </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr"/>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
+      <c r="L145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -3357,19 +4608,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>item_84</t>
+          <t>item_89</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>84. Enjoys reading books, newspapers, magazines</t>
-        </is>
-      </c>
+          <t>89. Performs responsible routine chores</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr"/>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="L146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -3377,155 +4636,199 @@
           <t>end group</t>
         </is>
       </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr"/>
+      <c r="L147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>begin group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>g_y12_15</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>12–15 Years</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>${show_all} = 'yes' or ${ca_band} &gt;= 13</t>
-        </is>
-      </c>
+          <t>item_1_score</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>if(${item_1} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr"/>
+      <c r="L148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>item_85</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>85. Plays difficult games</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>item_2_score</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr"/>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr"/>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>if(${item_2} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr"/>
+      <c r="L149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>item_86</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>86. Exercises complete care for dress</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>item_3_score</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr"/>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr"/>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>if(${item_3} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr"/>
+      <c r="L150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>item_87</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>87. Buys own clothing accessories*</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>item_4_score</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>if(${item_4} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr"/>
+      <c r="L151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>item_88</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>88. Engages in adolescent group activities*</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>Speech/Language-related</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>item_5_score</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr"/>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>if(${item_5} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>select_one vsms_response</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>item_89</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>89. Performs responsible routine chores</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>item_6_score</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>if(${item_6} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>end group</t>
-        </is>
-      </c>
+          <t>calculate</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>item_7_score</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>if(${item_7} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3535,14 +4838,23 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>item_1_score</t>
-        </is>
-      </c>
+          <t>item_8_score</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr">
         <is>
-          <t>if(${item_1} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_8} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3552,14 +4864,23 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>item_2_score</t>
-        </is>
-      </c>
+          <t>item_9_score</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr"/>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
       <c r="J156" t="inlineStr">
         <is>
-          <t>if(${item_2} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_9} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3569,14 +4890,23 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>item_3_score</t>
-        </is>
-      </c>
+          <t>item_10_score</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr"/>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr">
         <is>
-          <t>if(${item_3} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_10} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3586,14 +4916,23 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>item_4_score</t>
-        </is>
-      </c>
+          <t>item_11_score</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr"/>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr">
         <is>
-          <t>if(${item_4} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_11} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3603,14 +4942,23 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>item_5_score</t>
-        </is>
-      </c>
+          <t>item_12_score</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
       <c r="J159" t="inlineStr">
         <is>
-          <t>if(${item_5} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_12} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr"/>
+      <c r="L159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3620,14 +4968,23 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>item_6_score</t>
-        </is>
-      </c>
+          <t>item_13_score</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr">
         <is>
-          <t>if(${item_6} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_13} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3637,14 +4994,23 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>item_7_score</t>
-        </is>
-      </c>
+          <t>item_14_score</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr"/>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr"/>
+      <c r="I161" t="inlineStr"/>
       <c r="J161" t="inlineStr">
         <is>
-          <t>if(${item_7} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_14} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3654,14 +5020,23 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>item_8_score</t>
-        </is>
-      </c>
+          <t>item_15_score</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr"/>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr"/>
+      <c r="I162" t="inlineStr"/>
       <c r="J162" t="inlineStr">
         <is>
-          <t>if(${item_8} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_15} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3671,14 +5046,23 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>item_9_score</t>
-        </is>
-      </c>
+          <t>item_16_score</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr">
         <is>
-          <t>if(${item_9} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_16} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3688,14 +5072,23 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>item_10_score</t>
-        </is>
-      </c>
+          <t>item_17_score</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr"/>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
+      <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr">
         <is>
-          <t>if(${item_10} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_17} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3705,14 +5098,23 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>item_11_score</t>
-        </is>
-      </c>
+          <t>item_18_score</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr"/>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr"/>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr">
         <is>
-          <t>if(${item_11} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_18} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3722,14 +5124,23 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>item_12_score</t>
-        </is>
-      </c>
+          <t>item_19_score</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr"/>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
+      <c r="H166" t="inlineStr"/>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr">
         <is>
-          <t>if(${item_12} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_19} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3739,14 +5150,23 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>item_13_score</t>
-        </is>
-      </c>
+          <t>item_20_score</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr"/>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr"/>
+      <c r="H167" t="inlineStr"/>
+      <c r="I167" t="inlineStr"/>
       <c r="J167" t="inlineStr">
         <is>
-          <t>if(${item_13} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_20} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -3756,14 +5176,23 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>item_14_score</t>
-        </is>
-      </c>
+          <t>item_21_score</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr"/>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
+      <c r="I168" t="inlineStr"/>
       <c r="J168" t="inlineStr">
         <is>
-          <t>if(${item_14} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_21} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -3773,14 +5202,23 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>item_15_score</t>
-        </is>
-      </c>
+          <t>item_22_score</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr"/>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr"/>
+      <c r="I169" t="inlineStr"/>
       <c r="J169" t="inlineStr">
         <is>
-          <t>if(${item_15} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_22} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -3790,14 +5228,23 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>item_16_score</t>
-        </is>
-      </c>
+          <t>item_23_score</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr"/>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
+      <c r="H170" t="inlineStr"/>
+      <c r="I170" t="inlineStr"/>
       <c r="J170" t="inlineStr">
         <is>
-          <t>if(${item_16} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_23} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr"/>
+      <c r="L170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -3807,14 +5254,23 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>item_17_score</t>
-        </is>
-      </c>
+          <t>item_24_score</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr"/>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr"/>
+      <c r="H171" t="inlineStr"/>
+      <c r="I171" t="inlineStr"/>
       <c r="J171" t="inlineStr">
         <is>
-          <t>if(${item_17} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_24} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
+      <c r="L171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -3824,14 +5280,23 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>item_18_score</t>
-        </is>
-      </c>
+          <t>item_25_score</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr"/>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
+      <c r="I172" t="inlineStr"/>
       <c r="J172" t="inlineStr">
         <is>
-          <t>if(${item_18} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_25} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3841,14 +5306,23 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>item_19_score</t>
-        </is>
-      </c>
+          <t>item_26_score</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
       <c r="J173" t="inlineStr">
         <is>
-          <t>if(${item_19} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_26} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr"/>
+      <c r="L173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3858,14 +5332,23 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>item_20_score</t>
-        </is>
-      </c>
+          <t>item_27_score</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr"/>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
+      <c r="I174" t="inlineStr"/>
       <c r="J174" t="inlineStr">
         <is>
-          <t>if(${item_20} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_27} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3875,14 +5358,23 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>item_21_score</t>
-        </is>
-      </c>
+          <t>item_28_score</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr"/>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
+      <c r="I175" t="inlineStr"/>
       <c r="J175" t="inlineStr">
         <is>
-          <t>if(${item_21} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_28} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr"/>
+      <c r="L175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3892,14 +5384,23 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>item_22_score</t>
-        </is>
-      </c>
+          <t>item_29_score</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
       <c r="J176" t="inlineStr">
         <is>
-          <t>if(${item_22} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_29} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr"/>
+      <c r="L176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3909,14 +5410,23 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>item_23_score</t>
-        </is>
-      </c>
+          <t>item_30_score</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr"/>
       <c r="J177" t="inlineStr">
         <is>
-          <t>if(${item_23} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_30} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr"/>
+      <c r="L177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3926,14 +5436,23 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>item_24_score</t>
-        </is>
-      </c>
+          <t>item_31_score</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr"/>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr"/>
+      <c r="I178" t="inlineStr"/>
       <c r="J178" t="inlineStr">
         <is>
-          <t>if(${item_24} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_31} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
+      <c r="L178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3943,14 +5462,23 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>item_25_score</t>
-        </is>
-      </c>
+          <t>item_32_score</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr"/>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr"/>
+      <c r="I179" t="inlineStr"/>
       <c r="J179" t="inlineStr">
         <is>
-          <t>if(${item_25} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_32} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr"/>
+      <c r="L179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3960,14 +5488,23 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>item_26_score</t>
-        </is>
-      </c>
+          <t>item_33_score</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
       <c r="J180" t="inlineStr">
         <is>
-          <t>if(${item_26} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_33} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr"/>
+      <c r="L180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3977,14 +5514,23 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>item_27_score</t>
-        </is>
-      </c>
+          <t>item_34_score</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr"/>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr"/>
+      <c r="I181" t="inlineStr"/>
       <c r="J181" t="inlineStr">
         <is>
-          <t>if(${item_27} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_34} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr"/>
+      <c r="L181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3994,14 +5540,23 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>item_28_score</t>
-        </is>
-      </c>
+          <t>item_35_score</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr"/>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr"/>
+      <c r="I182" t="inlineStr"/>
       <c r="J182" t="inlineStr">
         <is>
-          <t>if(${item_28} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_35} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr"/>
+      <c r="L182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -4011,14 +5566,23 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>item_29_score</t>
-        </is>
-      </c>
+          <t>item_36_score</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr"/>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr"/>
+      <c r="I183" t="inlineStr"/>
       <c r="J183" t="inlineStr">
         <is>
-          <t>if(${item_29} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_36} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr"/>
+      <c r="L183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -4028,14 +5592,23 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>item_30_score</t>
-        </is>
-      </c>
+          <t>item_37_score</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
       <c r="J184" t="inlineStr">
         <is>
-          <t>if(${item_30} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_37} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr"/>
+      <c r="L184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -4045,14 +5618,23 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>item_31_score</t>
-        </is>
-      </c>
+          <t>item_38_score</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr"/>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr"/>
+      <c r="I185" t="inlineStr"/>
       <c r="J185" t="inlineStr">
         <is>
-          <t>if(${item_31} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_38} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr"/>
+      <c r="L185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -4062,14 +5644,23 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>item_32_score</t>
-        </is>
-      </c>
+          <t>item_39_score</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
+      <c r="I186" t="inlineStr"/>
       <c r="J186" t="inlineStr">
         <is>
-          <t>if(${item_32} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_39} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr"/>
+      <c r="L186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -4079,14 +5670,23 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>item_33_score</t>
-        </is>
-      </c>
+          <t>item_40_score</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
       <c r="J187" t="inlineStr">
         <is>
-          <t>if(${item_33} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_40} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
+      <c r="L187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -4096,14 +5696,23 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>item_34_score</t>
-        </is>
-      </c>
+          <t>item_41_score</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
+      <c r="I188" t="inlineStr"/>
       <c r="J188" t="inlineStr">
         <is>
-          <t>if(${item_34} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_41} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr"/>
+      <c r="L188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -4113,14 +5722,23 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>item_35_score</t>
-        </is>
-      </c>
+          <t>item_42_score</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr"/>
+      <c r="I189" t="inlineStr"/>
       <c r="J189" t="inlineStr">
         <is>
-          <t>if(${item_35} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_42} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr"/>
+      <c r="L189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -4130,14 +5748,23 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>item_36_score</t>
-        </is>
-      </c>
+          <t>item_43_score</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr"/>
+      <c r="I190" t="inlineStr"/>
       <c r="J190" t="inlineStr">
         <is>
-          <t>if(${item_36} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_43} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr"/>
+      <c r="L190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -4147,14 +5774,23 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>item_37_score</t>
-        </is>
-      </c>
+          <t>item_44_score</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
       <c r="J191" t="inlineStr">
         <is>
-          <t>if(${item_37} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_44} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr"/>
+      <c r="L191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -4164,14 +5800,23 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>item_38_score</t>
-        </is>
-      </c>
+          <t>item_45_score</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr"/>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr"/>
+      <c r="I192" t="inlineStr"/>
       <c r="J192" t="inlineStr">
         <is>
-          <t>if(${item_38} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_45} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr"/>
+      <c r="L192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -4181,14 +5826,23 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>item_39_score</t>
-        </is>
-      </c>
+          <t>item_46_score</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr"/>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr"/>
+      <c r="H193" t="inlineStr"/>
+      <c r="I193" t="inlineStr"/>
       <c r="J193" t="inlineStr">
         <is>
-          <t>if(${item_39} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_46} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr"/>
+      <c r="L193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -4198,14 +5852,23 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>item_40_score</t>
-        </is>
-      </c>
+          <t>item_47_score</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
       <c r="J194" t="inlineStr">
         <is>
-          <t>if(${item_40} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_47} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
+      <c r="L194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -4215,14 +5878,23 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>item_41_score</t>
-        </is>
-      </c>
+          <t>item_48_score</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr"/>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr"/>
+      <c r="H195" t="inlineStr"/>
+      <c r="I195" t="inlineStr"/>
       <c r="J195" t="inlineStr">
         <is>
-          <t>if(${item_41} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_48} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr"/>
+      <c r="L195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -4232,14 +5904,23 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>item_42_score</t>
-        </is>
-      </c>
+          <t>item_49_score</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr"/>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr"/>
+      <c r="H196" t="inlineStr"/>
+      <c r="I196" t="inlineStr"/>
       <c r="J196" t="inlineStr">
         <is>
-          <t>if(${item_42} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_49} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr"/>
+      <c r="L196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -4249,14 +5930,23 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>item_43_score</t>
-        </is>
-      </c>
+          <t>item_50_score</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr"/>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr"/>
+      <c r="H197" t="inlineStr"/>
+      <c r="I197" t="inlineStr"/>
       <c r="J197" t="inlineStr">
         <is>
-          <t>if(${item_43} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_50} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr"/>
+      <c r="L197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -4266,14 +5956,23 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>item_44_score</t>
-        </is>
-      </c>
+          <t>item_51_score</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr"/>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr"/>
+      <c r="H198" t="inlineStr"/>
+      <c r="I198" t="inlineStr"/>
       <c r="J198" t="inlineStr">
         <is>
-          <t>if(${item_44} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_51} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
+      <c r="L198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -4283,14 +5982,23 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>item_45_score</t>
-        </is>
-      </c>
+          <t>item_52_score</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr"/>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr"/>
+      <c r="H199" t="inlineStr"/>
+      <c r="I199" t="inlineStr"/>
       <c r="J199" t="inlineStr">
         <is>
-          <t>if(${item_45} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_52} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr"/>
+      <c r="L199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -4300,14 +6008,23 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>item_46_score</t>
-        </is>
-      </c>
+          <t>item_53_score</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr"/>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr"/>
+      <c r="H200" t="inlineStr"/>
+      <c r="I200" t="inlineStr"/>
       <c r="J200" t="inlineStr">
         <is>
-          <t>if(${item_46} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_53} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr"/>
+      <c r="L200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -4317,14 +6034,23 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>item_47_score</t>
-        </is>
-      </c>
+          <t>item_54_score</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr"/>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr"/>
+      <c r="H201" t="inlineStr"/>
+      <c r="I201" t="inlineStr"/>
       <c r="J201" t="inlineStr">
         <is>
-          <t>if(${item_47} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_54} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr"/>
+      <c r="L201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -4334,14 +6060,23 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>item_48_score</t>
-        </is>
-      </c>
+          <t>item_55_score</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
       <c r="J202" t="inlineStr">
         <is>
-          <t>if(${item_48} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_55} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr"/>
+      <c r="L202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -4351,14 +6086,23 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>item_49_score</t>
-        </is>
-      </c>
+          <t>item_56_score</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr"/>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr"/>
+      <c r="H203" t="inlineStr"/>
+      <c r="I203" t="inlineStr"/>
       <c r="J203" t="inlineStr">
         <is>
-          <t>if(${item_49} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_56} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
+      <c r="L203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -4368,14 +6112,23 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>item_50_score</t>
-        </is>
-      </c>
+          <t>item_57_score</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr"/>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr"/>
+      <c r="H204" t="inlineStr"/>
+      <c r="I204" t="inlineStr"/>
       <c r="J204" t="inlineStr">
         <is>
-          <t>if(${item_50} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_57} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K204" t="inlineStr"/>
+      <c r="L204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -4385,14 +6138,23 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>item_51_score</t>
-        </is>
-      </c>
+          <t>item_58_score</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr"/>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr"/>
+      <c r="H205" t="inlineStr"/>
+      <c r="I205" t="inlineStr"/>
       <c r="J205" t="inlineStr">
         <is>
-          <t>if(${item_51} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_58} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr"/>
+      <c r="L205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -4402,14 +6164,23 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>item_52_score</t>
-        </is>
-      </c>
+          <t>item_59_score</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr"/>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr"/>
+      <c r="H206" t="inlineStr"/>
+      <c r="I206" t="inlineStr"/>
       <c r="J206" t="inlineStr">
         <is>
-          <t>if(${item_52} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_59} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
+      <c r="L206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -4419,14 +6190,23 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>item_53_score</t>
-        </is>
-      </c>
+          <t>item_60_score</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
       <c r="J207" t="inlineStr">
         <is>
-          <t>if(${item_53} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_60} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K207" t="inlineStr"/>
+      <c r="L207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -4436,14 +6216,23 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>item_54_score</t>
-        </is>
-      </c>
+          <t>item_61_score</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr"/>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
+      <c r="H208" t="inlineStr"/>
+      <c r="I208" t="inlineStr"/>
       <c r="J208" t="inlineStr">
         <is>
-          <t>if(${item_54} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_61} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K208" t="inlineStr"/>
+      <c r="L208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -4453,14 +6242,23 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>item_55_score</t>
-        </is>
-      </c>
+          <t>item_62_score</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
       <c r="J209" t="inlineStr">
         <is>
-          <t>if(${item_55} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_62} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr"/>
+      <c r="L209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -4470,14 +6268,23 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>item_56_score</t>
-        </is>
-      </c>
+          <t>item_63_score</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr"/>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr"/>
+      <c r="H210" t="inlineStr"/>
+      <c r="I210" t="inlineStr"/>
       <c r="J210" t="inlineStr">
         <is>
-          <t>if(${item_56} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_63} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
+      <c r="L210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -4487,14 +6294,23 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>item_57_score</t>
-        </is>
-      </c>
+          <t>item_64_score</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
       <c r="J211" t="inlineStr">
         <is>
-          <t>if(${item_57} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_64} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K211" t="inlineStr"/>
+      <c r="L211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -4504,14 +6320,23 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>item_58_score</t>
-        </is>
-      </c>
+          <t>item_65_score</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr"/>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr"/>
+      <c r="H212" t="inlineStr"/>
+      <c r="I212" t="inlineStr"/>
       <c r="J212" t="inlineStr">
         <is>
-          <t>if(${item_58} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_65} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K212" t="inlineStr"/>
+      <c r="L212" t="inlineStr"/>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -4521,14 +6346,23 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>item_59_score</t>
-        </is>
-      </c>
+          <t>item_66_score</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr"/>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr"/>
+      <c r="H213" t="inlineStr"/>
+      <c r="I213" t="inlineStr"/>
       <c r="J213" t="inlineStr">
         <is>
-          <t>if(${item_59} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_66} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr"/>
+      <c r="L213" t="inlineStr"/>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -4538,14 +6372,23 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>item_60_score</t>
-        </is>
-      </c>
+          <t>item_67_score</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
       <c r="J214" t="inlineStr">
         <is>
-          <t>if(${item_60} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_67} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
+      <c r="L214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -4555,14 +6398,23 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>item_61_score</t>
-        </is>
-      </c>
+          <t>item_68_score</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr"/>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr"/>
+      <c r="H215" t="inlineStr"/>
+      <c r="I215" t="inlineStr"/>
       <c r="J215" t="inlineStr">
         <is>
-          <t>if(${item_61} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_68} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K215" t="inlineStr"/>
+      <c r="L215" t="inlineStr"/>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -4572,14 +6424,23 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>item_62_score</t>
-        </is>
-      </c>
+          <t>item_69_score</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr"/>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr"/>
+      <c r="H216" t="inlineStr"/>
+      <c r="I216" t="inlineStr"/>
       <c r="J216" t="inlineStr">
         <is>
-          <t>if(${item_62} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_69} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K216" t="inlineStr"/>
+      <c r="L216" t="inlineStr"/>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -4589,14 +6450,23 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>item_63_score</t>
-        </is>
-      </c>
+          <t>item_70_score</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr"/>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
+      <c r="I217" t="inlineStr"/>
       <c r="J217" t="inlineStr">
         <is>
-          <t>if(${item_63} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_70} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K217" t="inlineStr"/>
+      <c r="L217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -4606,14 +6476,23 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>item_64_score</t>
-        </is>
-      </c>
+          <t>item_71_score</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr"/>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr"/>
+      <c r="H218" t="inlineStr"/>
+      <c r="I218" t="inlineStr"/>
       <c r="J218" t="inlineStr">
         <is>
-          <t>if(${item_64} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_71} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr"/>
+      <c r="L218" t="inlineStr"/>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -4623,14 +6502,23 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>item_65_score</t>
-        </is>
-      </c>
+          <t>item_72_score</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr"/>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
+      <c r="I219" t="inlineStr"/>
       <c r="J219" t="inlineStr">
         <is>
-          <t>if(${item_65} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_72} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
+      <c r="L219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -4640,14 +6528,23 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>item_66_score</t>
-        </is>
-      </c>
+          <t>item_73_score</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr"/>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr"/>
+      <c r="H220" t="inlineStr"/>
+      <c r="I220" t="inlineStr"/>
       <c r="J220" t="inlineStr">
         <is>
-          <t>if(${item_66} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_73} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr"/>
+      <c r="L220" t="inlineStr"/>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -4657,14 +6554,23 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>item_67_score</t>
-        </is>
-      </c>
+          <t>item_74_score</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr"/>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr"/>
+      <c r="H221" t="inlineStr"/>
+      <c r="I221" t="inlineStr"/>
       <c r="J221" t="inlineStr">
         <is>
-          <t>if(${item_67} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_74} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
+      <c r="L221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -4674,14 +6580,23 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>item_68_score</t>
-        </is>
-      </c>
+          <t>item_75_score</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr"/>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr"/>
+      <c r="H222" t="inlineStr"/>
+      <c r="I222" t="inlineStr"/>
       <c r="J222" t="inlineStr">
         <is>
-          <t>if(${item_68} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_75} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K222" t="inlineStr"/>
+      <c r="L222" t="inlineStr"/>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -4691,14 +6606,23 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>item_69_score</t>
-        </is>
-      </c>
+          <t>item_76_score</t>
+        </is>
+      </c>
+      <c r="C223" t="inlineStr"/>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr"/>
+      <c r="H223" t="inlineStr"/>
+      <c r="I223" t="inlineStr"/>
       <c r="J223" t="inlineStr">
         <is>
-          <t>if(${item_69} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_76} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K223" t="inlineStr"/>
+      <c r="L223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -4708,14 +6632,23 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>item_70_score</t>
-        </is>
-      </c>
+          <t>item_77_score</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr"/>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr"/>
+      <c r="H224" t="inlineStr"/>
+      <c r="I224" t="inlineStr"/>
       <c r="J224" t="inlineStr">
         <is>
-          <t>if(${item_70} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_77} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K224" t="inlineStr"/>
+      <c r="L224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -4725,14 +6658,23 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>item_71_score</t>
-        </is>
-      </c>
+          <t>item_78_score</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr"/>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr"/>
+      <c r="H225" t="inlineStr"/>
+      <c r="I225" t="inlineStr"/>
       <c r="J225" t="inlineStr">
         <is>
-          <t>if(${item_71} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_78} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr"/>
+      <c r="L225" t="inlineStr"/>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -4742,14 +6684,23 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>item_72_score</t>
-        </is>
-      </c>
+          <t>item_79_score</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
       <c r="J226" t="inlineStr">
         <is>
-          <t>if(${item_72} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_79} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K226" t="inlineStr"/>
+      <c r="L226" t="inlineStr"/>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -4759,14 +6710,23 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>item_73_score</t>
-        </is>
-      </c>
+          <t>item_80_score</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr"/>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr"/>
+      <c r="H227" t="inlineStr"/>
+      <c r="I227" t="inlineStr"/>
       <c r="J227" t="inlineStr">
         <is>
-          <t>if(${item_73} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_80} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K227" t="inlineStr"/>
+      <c r="L227" t="inlineStr"/>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -4776,14 +6736,23 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>item_74_score</t>
-        </is>
-      </c>
+          <t>item_81_score</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
       <c r="J228" t="inlineStr">
         <is>
-          <t>if(${item_74} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_81} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K228" t="inlineStr"/>
+      <c r="L228" t="inlineStr"/>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -4793,14 +6762,23 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>item_75_score</t>
-        </is>
-      </c>
+          <t>item_82_score</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr"/>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr"/>
+      <c r="H229" t="inlineStr"/>
+      <c r="I229" t="inlineStr"/>
       <c r="J229" t="inlineStr">
         <is>
-          <t>if(${item_75} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_82} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K229" t="inlineStr"/>
+      <c r="L229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -4810,14 +6788,23 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>item_76_score</t>
-        </is>
-      </c>
+          <t>item_83_score</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
       <c r="J230" t="inlineStr">
         <is>
-          <t>if(${item_76} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_83} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
+      <c r="L230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -4827,14 +6814,23 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>item_77_score</t>
-        </is>
-      </c>
+          <t>item_84_score</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr"/>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr"/>
+      <c r="H231" t="inlineStr"/>
+      <c r="I231" t="inlineStr"/>
       <c r="J231" t="inlineStr">
         <is>
-          <t>if(${item_77} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_84} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K231" t="inlineStr"/>
+      <c r="L231" t="inlineStr"/>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -4844,14 +6840,23 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>item_78_score</t>
-        </is>
-      </c>
+          <t>item_85_score</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr"/>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr"/>
+      <c r="H232" t="inlineStr"/>
+      <c r="I232" t="inlineStr"/>
       <c r="J232" t="inlineStr">
         <is>
-          <t>if(${item_78} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_85} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K232" t="inlineStr"/>
+      <c r="L232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -4861,14 +6866,23 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>item_79_score</t>
-        </is>
-      </c>
+          <t>item_86_score</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr"/>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr"/>
+      <c r="H233" t="inlineStr"/>
+      <c r="I233" t="inlineStr"/>
       <c r="J233" t="inlineStr">
         <is>
-          <t>if(${item_79} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_86} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K233" t="inlineStr"/>
+      <c r="L233" t="inlineStr"/>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -4878,14 +6892,23 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>item_80_score</t>
-        </is>
-      </c>
+          <t>item_87_score</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr"/>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr"/>
+      <c r="H234" t="inlineStr"/>
+      <c r="I234" t="inlineStr"/>
       <c r="J234" t="inlineStr">
         <is>
-          <t>if(${item_80} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_87} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K234" t="inlineStr"/>
+      <c r="L234" t="inlineStr"/>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -4895,14 +6918,23 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>item_81_score</t>
-        </is>
-      </c>
+          <t>item_88_score</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr"/>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr"/>
+      <c r="H235" t="inlineStr"/>
+      <c r="I235" t="inlineStr"/>
       <c r="J235" t="inlineStr">
         <is>
-          <t>if(${item_81} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_88} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K235" t="inlineStr"/>
+      <c r="L235" t="inlineStr"/>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -4912,14 +6944,23 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>item_82_score</t>
-        </is>
-      </c>
+          <t>item_89_score</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr"/>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr"/>
+      <c r="H236" t="inlineStr"/>
+      <c r="I236" t="inlineStr"/>
       <c r="J236" t="inlineStr">
         <is>
-          <t>if(${item_82} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_89} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K236" t="inlineStr"/>
+      <c r="L236" t="inlineStr"/>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -4929,14 +6970,23 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>item_83_score</t>
-        </is>
-      </c>
+          <t>raw_score</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr"/>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr"/>
+      <c r="H237" t="inlineStr"/>
+      <c r="I237" t="inlineStr"/>
       <c r="J237" t="inlineStr">
         <is>
-          <t>if(${item_83} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>${item_1_score} + ${item_2_score} + ${item_3_score} + ${item_4_score} + ${item_5_score} + ${item_6_score} + ${item_7_score} + ${item_8_score} + ${item_9_score} + ${item_10_score} + ${item_11_score} + ${item_12_score} + ${item_13_score} + ${item_14_score} + ${item_15_score} + ${item_16_score} + ${item_17_score} + ${item_18_score} + ${item_19_score} + ${item_20_score} + ${item_21_score} + ${item_22_score} + ${item_23_score} + ${item_24_score} + ${item_25_score} + ${item_26_score} + ${item_27_score} + ${item_28_score} + ${item_29_score} + ${item_30_score} + ${item_31_score} + ${item_32_score} + ${item_33_score} + ${item_34_score} + ${item_35_score} + ${item_36_score} + ${item_37_score} + ${item_38_score} + ${item_39_score} + ${item_40_score} + ${item_41_score} + ${item_42_score} + ${item_43_score} + ${item_44_score} + ${item_45_score} + ${item_46_score} + ${item_47_score} + ${item_48_score} + ${item_49_score} + ${item_50_score} + ${item_51_score} + ${item_52_score} + ${item_53_score} + ${item_54_score} + ${item_55_score} + ${item_56_score} + ${item_57_score} + ${item_58_score} + ${item_59_score} + ${item_60_score} + ${item_61_score} + ${item_62_score} + ${item_63_score} + ${item_64_score} + ${item_65_score} + ${item_66_score} + ${item_67_score} + ${item_68_score} + ${item_69_score} + ${item_70_score} + ${item_71_score} + ${item_72_score} + ${item_73_score} + ${item_74_score} + ${item_75_score} + ${item_76_score} + ${item_77_score} + ${item_78_score} + ${item_79_score} + ${item_80_score} + ${item_81_score} + ${item_82_score} + ${item_83_score} + ${item_84_score} + ${item_85_score} + ${item_86_score} + ${item_87_score} + ${item_88_score} + ${item_89_score}</t>
+        </is>
+      </c>
+      <c r="K237" t="inlineStr"/>
+      <c r="L237" t="inlineStr"/>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -4946,14 +6996,23 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>item_84_score</t>
-        </is>
-      </c>
+          <t>total_yes_items</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr"/>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr"/>
+      <c r="H238" t="inlineStr"/>
+      <c r="I238" t="inlineStr"/>
       <c r="J238" t="inlineStr">
         <is>
-          <t>if(${item_84} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_1} = 'yes', 1, 0) + if(${item_2} = 'yes', 1, 0) + if(${item_3} = 'yes', 1, 0) + if(${item_4} = 'yes', 1, 0) + if(${item_5} = 'yes', 1, 0) + if(${item_6} = 'yes', 1, 0) + if(${item_7} = 'yes', 1, 0) + if(${item_8} = 'yes', 1, 0) + if(${item_9} = 'yes', 1, 0) + if(${item_10} = 'yes', 1, 0) + if(${item_11} = 'yes', 1, 0) + if(${item_12} = 'yes', 1, 0) + if(${item_13} = 'yes', 1, 0) + if(${item_14} = 'yes', 1, 0) + if(${item_15} = 'yes', 1, 0) + if(${item_16} = 'yes', 1, 0) + if(${item_17} = 'yes', 1, 0) + if(${item_18} = 'yes', 1, 0) + if(${item_19} = 'yes', 1, 0) + if(${item_20} = 'yes', 1, 0) + if(${item_21} = 'yes', 1, 0) + if(${item_22} = 'yes', 1, 0) + if(${item_23} = 'yes', 1, 0) + if(${item_24} = 'yes', 1, 0) + if(${item_25} = 'yes', 1, 0) + if(${item_26} = 'yes', 1, 0) + if(${item_27} = 'yes', 1, 0) + if(${item_28} = 'yes', 1, 0) + if(${item_29} = 'yes', 1, 0) + if(${item_30} = 'yes', 1, 0) + if(${item_31} = 'yes', 1, 0) + if(${item_32} = 'yes', 1, 0) + if(${item_33} = 'yes', 1, 0) + if(${item_34} = 'yes', 1, 0) + if(${item_35} = 'yes', 1, 0) + if(${item_36} = 'yes', 1, 0) + if(${item_37} = 'yes', 1, 0) + if(${item_38} = 'yes', 1, 0) + if(${item_39} = 'yes', 1, 0) + if(${item_40} = 'yes', 1, 0) + if(${item_41} = 'yes', 1, 0) + if(${item_42} = 'yes', 1, 0) + if(${item_43} = 'yes', 1, 0) + if(${item_44} = 'yes', 1, 0) + if(${item_45} = 'yes', 1, 0) + if(${item_46} = 'yes', 1, 0) + if(${item_47} = 'yes', 1, 0) + if(${item_48} = 'yes', 1, 0) + if(${item_49} = 'yes', 1, 0) + if(${item_50} = 'yes', 1, 0) + if(${item_51} = 'yes', 1, 0) + if(${item_52} = 'yes', 1, 0) + if(${item_53} = 'yes', 1, 0) + if(${item_54} = 'yes', 1, 0) + if(${item_55} = 'yes', 1, 0) + if(${item_56} = 'yes', 1, 0) + if(${item_57} = 'yes', 1, 0) + if(${item_58} = 'yes', 1, 0) + if(${item_59} = 'yes', 1, 0) + if(${item_60} = 'yes', 1, 0) + if(${item_61} = 'yes', 1, 0) + if(${item_62} = 'yes', 1, 0) + if(${item_63} = 'yes', 1, 0) + if(${item_64} = 'yes', 1, 0) + if(${item_65} = 'yes', 1, 0) + if(${item_66} = 'yes', 1, 0) + if(${item_67} = 'yes', 1, 0) + if(${item_68} = 'yes', 1, 0) + if(${item_69} = 'yes', 1, 0) + if(${item_70} = 'yes', 1, 0) + if(${item_71} = 'yes', 1, 0) + if(${item_72} = 'yes', 1, 0) + if(${item_73} = 'yes', 1, 0) + if(${item_74} = 'yes', 1, 0) + if(${item_75} = 'yes', 1, 0) + if(${item_76} = 'yes', 1, 0) + if(${item_77} = 'yes', 1, 0) + if(${item_78} = 'yes', 1, 0) + if(${item_79} = 'yes', 1, 0) + if(${item_80} = 'yes', 1, 0) + if(${item_81} = 'yes', 1, 0) + if(${item_82} = 'yes', 1, 0) + if(${item_83} = 'yes', 1, 0) + if(${item_84} = 'yes', 1, 0) + if(${item_85} = 'yes', 1, 0) + if(${item_86} = 'yes', 1, 0) + if(${item_87} = 'yes', 1, 0) + if(${item_88} = 'yes', 1, 0) + if(${item_89} = 'yes', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K238" t="inlineStr"/>
+      <c r="L238" t="inlineStr"/>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -4963,14 +7022,23 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>item_85_score</t>
-        </is>
-      </c>
+          <t>total_no_items</t>
+        </is>
+      </c>
+      <c r="C239" t="inlineStr"/>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr"/>
+      <c r="H239" t="inlineStr"/>
+      <c r="I239" t="inlineStr"/>
       <c r="J239" t="inlineStr">
         <is>
-          <t>if(${item_85} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_1} = 'no', 1, 0) + if(${item_2} = 'no', 1, 0) + if(${item_3} = 'no', 1, 0) + if(${item_4} = 'no', 1, 0) + if(${item_5} = 'no', 1, 0) + if(${item_6} = 'no', 1, 0) + if(${item_7} = 'no', 1, 0) + if(${item_8} = 'no', 1, 0) + if(${item_9} = 'no', 1, 0) + if(${item_10} = 'no', 1, 0) + if(${item_11} = 'no', 1, 0) + if(${item_12} = 'no', 1, 0) + if(${item_13} = 'no', 1, 0) + if(${item_14} = 'no', 1, 0) + if(${item_15} = 'no', 1, 0) + if(${item_16} = 'no', 1, 0) + if(${item_17} = 'no', 1, 0) + if(${item_18} = 'no', 1, 0) + if(${item_19} = 'no', 1, 0) + if(${item_20} = 'no', 1, 0) + if(${item_21} = 'no', 1, 0) + if(${item_22} = 'no', 1, 0) + if(${item_23} = 'no', 1, 0) + if(${item_24} = 'no', 1, 0) + if(${item_25} = 'no', 1, 0) + if(${item_26} = 'no', 1, 0) + if(${item_27} = 'no', 1, 0) + if(${item_28} = 'no', 1, 0) + if(${item_29} = 'no', 1, 0) + if(${item_30} = 'no', 1, 0) + if(${item_31} = 'no', 1, 0) + if(${item_32} = 'no', 1, 0) + if(${item_33} = 'no', 1, 0) + if(${item_34} = 'no', 1, 0) + if(${item_35} = 'no', 1, 0) + if(${item_36} = 'no', 1, 0) + if(${item_37} = 'no', 1, 0) + if(${item_38} = 'no', 1, 0) + if(${item_39} = 'no', 1, 0) + if(${item_40} = 'no', 1, 0) + if(${item_41} = 'no', 1, 0) + if(${item_42} = 'no', 1, 0) + if(${item_43} = 'no', 1, 0) + if(${item_44} = 'no', 1, 0) + if(${item_45} = 'no', 1, 0) + if(${item_46} = 'no', 1, 0) + if(${item_47} = 'no', 1, 0) + if(${item_48} = 'no', 1, 0) + if(${item_49} = 'no', 1, 0) + if(${item_50} = 'no', 1, 0) + if(${item_51} = 'no', 1, 0) + if(${item_52} = 'no', 1, 0) + if(${item_53} = 'no', 1, 0) + if(${item_54} = 'no', 1, 0) + if(${item_55} = 'no', 1, 0) + if(${item_56} = 'no', 1, 0) + if(${item_57} = 'no', 1, 0) + if(${item_58} = 'no', 1, 0) + if(${item_59} = 'no', 1, 0) + if(${item_60} = 'no', 1, 0) + if(${item_61} = 'no', 1, 0) + if(${item_62} = 'no', 1, 0) + if(${item_63} = 'no', 1, 0) + if(${item_64} = 'no', 1, 0) + if(${item_65} = 'no', 1, 0) + if(${item_66} = 'no', 1, 0) + if(${item_67} = 'no', 1, 0) + if(${item_68} = 'no', 1, 0) + if(${item_69} = 'no', 1, 0) + if(${item_70} = 'no', 1, 0) + if(${item_71} = 'no', 1, 0) + if(${item_72} = 'no', 1, 0) + if(${item_73} = 'no', 1, 0) + if(${item_74} = 'no', 1, 0) + if(${item_75} = 'no', 1, 0) + if(${item_76} = 'no', 1, 0) + if(${item_77} = 'no', 1, 0) + if(${item_78} = 'no', 1, 0) + if(${item_79} = 'no', 1, 0) + if(${item_80} = 'no', 1, 0) + if(${item_81} = 'no', 1, 0) + if(${item_82} = 'no', 1, 0) + if(${item_83} = 'no', 1, 0) + if(${item_84} = 'no', 1, 0) + if(${item_85} = 'no', 1, 0) + if(${item_86} = 'no', 1, 0) + if(${item_87} = 'no', 1, 0) + if(${item_88} = 'no', 1, 0) + if(${item_89} = 'no', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K239" t="inlineStr"/>
+      <c r="L239" t="inlineStr"/>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -4980,14 +7048,23 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>item_86_score</t>
-        </is>
-      </c>
+          <t>total_not_assessed_items</t>
+        </is>
+      </c>
+      <c r="C240" t="inlineStr"/>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr"/>
+      <c r="H240" t="inlineStr"/>
+      <c r="I240" t="inlineStr"/>
       <c r="J240" t="inlineStr">
         <is>
-          <t>if(${item_86} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${item_1} = 'not_assessed', 1, 0) + if(${item_2} = 'not_assessed', 1, 0) + if(${item_3} = 'not_assessed', 1, 0) + if(${item_4} = 'not_assessed', 1, 0) + if(${item_5} = 'not_assessed', 1, 0) + if(${item_6} = 'not_assessed', 1, 0) + if(${item_7} = 'not_assessed', 1, 0) + if(${item_8} = 'not_assessed', 1, 0) + if(${item_9} = 'not_assessed', 1, 0) + if(${item_10} = 'not_assessed', 1, 0) + if(${item_11} = 'not_assessed', 1, 0) + if(${item_12} = 'not_assessed', 1, 0) + if(${item_13} = 'not_assessed', 1, 0) + if(${item_14} = 'not_assessed', 1, 0) + if(${item_15} = 'not_assessed', 1, 0) + if(${item_16} = 'not_assessed', 1, 0) + if(${item_17} = 'not_assessed', 1, 0) + if(${item_18} = 'not_assessed', 1, 0) + if(${item_19} = 'not_assessed', 1, 0) + if(${item_20} = 'not_assessed', 1, 0) + if(${item_21} = 'not_assessed', 1, 0) + if(${item_22} = 'not_assessed', 1, 0) + if(${item_23} = 'not_assessed', 1, 0) + if(${item_24} = 'not_assessed', 1, 0) + if(${item_25} = 'not_assessed', 1, 0) + if(${item_26} = 'not_assessed', 1, 0) + if(${item_27} = 'not_assessed', 1, 0) + if(${item_28} = 'not_assessed', 1, 0) + if(${item_29} = 'not_assessed', 1, 0) + if(${item_30} = 'not_assessed', 1, 0) + if(${item_31} = 'not_assessed', 1, 0) + if(${item_32} = 'not_assessed', 1, 0) + if(${item_33} = 'not_assessed', 1, 0) + if(${item_34} = 'not_assessed', 1, 0) + if(${item_35} = 'not_assessed', 1, 0) + if(${item_36} = 'not_assessed', 1, 0) + if(${item_37} = 'not_assessed', 1, 0) + if(${item_38} = 'not_assessed', 1, 0) + if(${item_39} = 'not_assessed', 1, 0) + if(${item_40} = 'not_assessed', 1, 0) + if(${item_41} = 'not_assessed', 1, 0) + if(${item_42} = 'not_assessed', 1, 0) + if(${item_43} = 'not_assessed', 1, 0) + if(${item_44} = 'not_assessed', 1, 0) + if(${item_45} = 'not_assessed', 1, 0) + if(${item_46} = 'not_assessed', 1, 0) + if(${item_47} = 'not_assessed', 1, 0) + if(${item_48} = 'not_assessed', 1, 0) + if(${item_49} = 'not_assessed', 1, 0) + if(${item_50} = 'not_assessed', 1, 0) + if(${item_51} = 'not_assessed', 1, 0) + if(${item_52} = 'not_assessed', 1, 0) + if(${item_53} = 'not_assessed', 1, 0) + if(${item_54} = 'not_assessed', 1, 0) + if(${item_55} = 'not_assessed', 1, 0) + if(${item_56} = 'not_assessed', 1, 0) + if(${item_57} = 'not_assessed', 1, 0) + if(${item_58} = 'not_assessed', 1, 0) + if(${item_59} = 'not_assessed', 1, 0) + if(${item_60} = 'not_assessed', 1, 0) + if(${item_61} = 'not_assessed', 1, 0) + if(${item_62} = 'not_assessed', 1, 0) + if(${item_63} = 'not_assessed', 1, 0) + if(${item_64} = 'not_assessed', 1, 0) + if(${item_65} = 'not_assessed', 1, 0) + if(${item_66} = 'not_assessed', 1, 0) + if(${item_67} = 'not_assessed', 1, 0) + if(${item_68} = 'not_assessed', 1, 0) + if(${item_69} = 'not_assessed', 1, 0) + if(${item_70} = 'not_assessed', 1, 0) + if(${item_71} = 'not_assessed', 1, 0) + if(${item_72} = 'not_assessed', 1, 0) + if(${item_73} = 'not_assessed', 1, 0) + if(${item_74} = 'not_assessed', 1, 0) + if(${item_75} = 'not_assessed', 1, 0) + if(${item_76} = 'not_assessed', 1, 0) + if(${item_77} = 'not_assessed', 1, 0) + if(${item_78} = 'not_assessed', 1, 0) + if(${item_79} = 'not_assessed', 1, 0) + if(${item_80} = 'not_assessed', 1, 0) + if(${item_81} = 'not_assessed', 1, 0) + if(${item_82} = 'not_assessed', 1, 0) + if(${item_83} = 'not_assessed', 1, 0) + if(${item_84} = 'not_assessed', 1, 0) + if(${item_85} = 'not_assessed', 1, 0) + if(${item_86} = 'not_assessed', 1, 0) + if(${item_87} = 'not_assessed', 1, 0) + if(${item_88} = 'not_assessed', 1, 0) + if(${item_89} = 'not_assessed', 1, 0)</t>
+        </is>
+      </c>
+      <c r="K240" t="inlineStr"/>
+      <c r="L240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -4997,14 +7074,23 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>item_87_score</t>
-        </is>
-      </c>
+          <t>social_age_months</t>
+        </is>
+      </c>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
       <c r="J241" t="inlineStr">
         <is>
-          <t>if(${item_87} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${raw_score} = 0, 0, if(${raw_score} = 1, 1, if(${raw_score} = 2, 2, if(${raw_score} = 3, 3, if(${raw_score} = 4, 4, if(${raw_score} = 5, 5, if(${raw_score} = 6, 6, if(${raw_score} = 7, 7, if(${raw_score} = 8, 8, if(${raw_score} = 9, 9, if(${raw_score} = 10, 10, if(${raw_score} = 11, 11, if(${raw_score} = 12, 12, if(${raw_score} = 13, 13, if(${raw_score} = 14, 14, if(${raw_score} = 15, 15, if(${raw_score} = 16, 16, if(${raw_score} = 17, 17, if(${raw_score} = 18, 18, if(${raw_score} = 19, 19, if(${raw_score} = 20, 20, if(${raw_score} = 21, 21, if(${raw_score} = 22, 22, if(${raw_score} = 23, 23, if(${raw_score} = 24, 24, if(${raw_score} = 25, 25, if(${raw_score} = 26, 26, if(${raw_score} = 27, 27, if(${raw_score} = 28, 28, if(${raw_score} = 29, 29, if(${raw_score} = 30, 30, if(${raw_score} = 31, 31, if(${raw_score} = 32, 32, if(${raw_score} = 33, 33, if(${raw_score} = 34, 34, if(${raw_score} = 35, 35, if(${raw_score} = 36, 36, if(${raw_score} = 37, 37, if(${raw_score} = 38, 38, if(${raw_score} = 39, 39, if(${raw_score} = 40, 40, if(${raw_score} = 41, 41, if(${raw_score} = 42, 42, if(${raw_score} = 43, 43, if(${raw_score} = 44, 44, if(${raw_score} = 45, 45, if(${raw_score} = 46, 46, if(${raw_score} = 47, 47, if(${raw_score} = 48, 48, if(${raw_score} = 49, 49, if(${raw_score} = 50, 50, if(${raw_score} = 51, 51, if(${raw_score} = 52, 52, if(${raw_score} = 53, 53, if(${raw_score} = 54, 54, if(${raw_score} = 55, 55, if(${raw_score} = 56, 56, if(${raw_score} = 57, 57, if(${raw_score} = 58, 58, if(${raw_score} = 59, 59, if(${raw_score} = 60, 60, if(${raw_score} = 61, 61, if(${raw_score} = 62, 62, if(${raw_score} = 63, 63, if(${raw_score} = 64, 64, if(${raw_score} = 65, 65, if(${raw_score} = 66, 66, if(${raw_score} = 67, 67, if(${raw_score} = 68, 68, if(${raw_score} = 69, 69, if(${raw_score} = 70, 70, if(${raw_score} = 71, 71, if(${raw_score} = 72, 72, if(${raw_score} = 73, 73, if(${raw_score} = 74, 74, if(${raw_score} = 75, 75, if(${raw_score} = 76, 76, if(${raw_score} = 77, 77, if(${raw_score} = 78, 78, if(${raw_score} = 79, 79, if(${raw_score} = 80, 80, if(${raw_score} = 81, 81, if(${raw_score} = 82, 82, if(${raw_score} = 83, 83, if(${raw_score} = 84, 84, if(${raw_score} = 85, 85, if(${raw_score} = 86, 86, if(${raw_score} = 87, 87, if(${raw_score} = 88, 88, if(${raw_score} = 89, 89, 0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
+        </is>
+      </c>
+      <c r="K241" t="inlineStr"/>
+      <c r="L241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -5014,14 +7100,23 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>item_88_score</t>
-        </is>
-      </c>
+          <t>social_age_years</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr"/>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr"/>
+      <c r="H242" t="inlineStr"/>
+      <c r="I242" t="inlineStr"/>
       <c r="J242" t="inlineStr">
         <is>
-          <t>if(${item_88} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>floor(${social_age_months} div 12)</t>
+        </is>
+      </c>
+      <c r="K242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -5031,14 +7126,23 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>item_89_score</t>
-        </is>
-      </c>
+          <t>social_age_remaining_months</t>
+        </is>
+      </c>
+      <c r="C243" t="inlineStr"/>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr"/>
+      <c r="H243" t="inlineStr"/>
+      <c r="I243" t="inlineStr"/>
       <c r="J243" t="inlineStr">
         <is>
-          <t>if(${item_89} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>${social_age_months} - (${social_age_years} * 12)</t>
+        </is>
+      </c>
+      <c r="K243" t="inlineStr"/>
+      <c r="L243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -5048,14 +7152,23 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>raw_score</t>
-        </is>
-      </c>
+          <t>social_quotient_raw</t>
+        </is>
+      </c>
+      <c r="C244" t="inlineStr"/>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr"/>
+      <c r="H244" t="inlineStr"/>
+      <c r="I244" t="inlineStr"/>
       <c r="J244" t="inlineStr">
         <is>
-          <t>${item_1_score} + ${item_2_score} + ${item_3_score} + ${item_4_score} + ${item_5_score} + ${item_6_score} + ${item_7_score} + ${item_8_score} + ${item_9_score} + ${item_10_score} + ${item_11_score} + ${item_12_score} + ${item_13_score} + ${item_14_score} + ${item_15_score} + ${item_16_score} + ${item_17_score} + ${item_18_score} + ${item_19_score} + ${item_20_score} + ${item_21_score} + ${item_22_score} + ${item_23_score} + ${item_24_score} + ${item_25_score} + ${item_26_score} + ${item_27_score} + ${item_28_score} + ${item_29_score} + ${item_30_score} + ${item_31_score} + ${item_32_score} + ${item_33_score} + ${item_34_score} + ${item_35_score} + ${item_36_score} + ${item_37_score} + ${item_38_score} + ${item_39_score} + ${item_40_score} + ${item_41_score} + ${item_42_score} + ${item_43_score} + ${item_44_score} + ${item_45_score} + ${item_46_score} + ${item_47_score} + ${item_48_score} + ${item_49_score} + ${item_50_score} + ${item_51_score} + ${item_52_score} + ${item_53_score} + ${item_54_score} + ${item_55_score} + ${item_56_score} + ${item_57_score} + ${item_58_score} + ${item_59_score} + ${item_60_score} + ${item_61_score} + ${item_62_score} + ${item_63_score} + ${item_64_score} + ${item_65_score} + ${item_66_score} + ${item_67_score} + ${item_68_score} + ${item_69_score} + ${item_70_score} + ${item_71_score} + ${item_72_score} + ${item_73_score} + ${item_74_score} + ${item_75_score} + ${item_76_score} + ${item_77_score} + ${item_78_score} + ${item_79_score} + ${item_80_score} + ${item_81_score} + ${item_82_score} + ${item_83_score} + ${item_84_score} + ${item_85_score} + ${item_86_score} + ${item_87_score} + ${item_88_score} + ${item_89_score}</t>
-        </is>
-      </c>
+          <t>if(${age_valid} = 'yes' and ${ca_months_dec} &gt; 0, ${social_age_months} div ${ca_months_dec} * 100, null)</t>
+        </is>
+      </c>
+      <c r="K244" t="inlineStr"/>
+      <c r="L244" t="inlineStr"/>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -5065,14 +7178,23 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>total_yes_items</t>
-        </is>
-      </c>
+          <t>social_quotient_rounded</t>
+        </is>
+      </c>
+      <c r="C245" t="inlineStr"/>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr"/>
+      <c r="H245" t="inlineStr"/>
+      <c r="I245" t="inlineStr"/>
       <c r="J245" t="inlineStr">
         <is>
-          <t>if(${item_1} = 'yes', 1, 0) + if(${item_2} = 'yes', 1, 0) + if(${item_3} = 'yes', 1, 0) + if(${item_4} = 'yes', 1, 0) + if(${item_5} = 'yes', 1, 0) + if(${item_6} = 'yes', 1, 0) + if(${item_7} = 'yes', 1, 0) + if(${item_8} = 'yes', 1, 0) + if(${item_9} = 'yes', 1, 0) + if(${item_10} = 'yes', 1, 0) + if(${item_11} = 'yes', 1, 0) + if(${item_12} = 'yes', 1, 0) + if(${item_13} = 'yes', 1, 0) + if(${item_14} = 'yes', 1, 0) + if(${item_15} = 'yes', 1, 0) + if(${item_16} = 'yes', 1, 0) + if(${item_17} = 'yes', 1, 0) + if(${item_18} = 'yes', 1, 0) + if(${item_19} = 'yes', 1, 0) + if(${item_20} = 'yes', 1, 0) + if(${item_21} = 'yes', 1, 0) + if(${item_22} = 'yes', 1, 0) + if(${item_23} = 'yes', 1, 0) + if(${item_24} = 'yes', 1, 0) + if(${item_25} = 'yes', 1, 0) + if(${item_26} = 'yes', 1, 0) + if(${item_27} = 'yes', 1, 0) + if(${item_28} = 'yes', 1, 0) + if(${item_29} = 'yes', 1, 0) + if(${item_30} = 'yes', 1, 0) + if(${item_31} = 'yes', 1, 0) + if(${item_32} = 'yes', 1, 0) + if(${item_33} = 'yes', 1, 0) + if(${item_34} = 'yes', 1, 0) + if(${item_35} = 'yes', 1, 0) + if(${item_36} = 'yes', 1, 0) + if(${item_37} = 'yes', 1, 0) + if(${item_38} = 'yes', 1, 0) + if(${item_39} = 'yes', 1, 0) + if(${item_40} = 'yes', 1, 0) + if(${item_41} = 'yes', 1, 0) + if(${item_42} = 'yes', 1, 0) + if(${item_43} = 'yes', 1, 0) + if(${item_44} = 'yes', 1, 0) + if(${item_45} = 'yes', 1, 0) + if(${item_46} = 'yes', 1, 0) + if(${item_47} = 'yes', 1, 0) + if(${item_48} = 'yes', 1, 0) + if(${item_49} = 'yes', 1, 0) + if(${item_50} = 'yes', 1, 0) + if(${item_51} = 'yes', 1, 0) + if(${item_52} = 'yes', 1, 0) + if(${item_53} = 'yes', 1, 0) + if(${item_54} = 'yes', 1, 0) + if(${item_55} = 'yes', 1, 0) + if(${item_56} = 'yes', 1, 0) + if(${item_57} = 'yes', 1, 0) + if(${item_58} = 'yes', 1, 0) + if(${item_59} = 'yes', 1, 0) + if(${item_60} = 'yes', 1, 0) + if(${item_61} = 'yes', 1, 0) + if(${item_62} = 'yes', 1, 0) + if(${item_63} = 'yes', 1, 0) + if(${item_64} = 'yes', 1, 0) + if(${item_65} = 'yes', 1, 0) + if(${item_66} = 'yes', 1, 0) + if(${item_67} = 'yes', 1, 0) + if(${item_68} = 'yes', 1, 0) + if(${item_69} = 'yes', 1, 0) + if(${item_70} = 'yes', 1, 0) + if(${item_71} = 'yes', 1, 0) + if(${item_72} = 'yes', 1, 0) + if(${item_73} = 'yes', 1, 0) + if(${item_74} = 'yes', 1, 0) + if(${item_75} = 'yes', 1, 0) + if(${item_76} = 'yes', 1, 0) + if(${item_77} = 'yes', 1, 0) + if(${item_78} = 'yes', 1, 0) + if(${item_79} = 'yes', 1, 0) + if(${item_80} = 'yes', 1, 0) + if(${item_81} = 'yes', 1, 0) + if(${item_82} = 'yes', 1, 0) + if(${item_83} = 'yes', 1, 0) + if(${item_84} = 'yes', 1, 0) + if(${item_85} = 'yes', 1, 0) + if(${item_86} = 'yes', 1, 0) + if(${item_87} = 'yes', 1, 0) + if(${item_88} = 'yes', 1, 0) + if(${item_89} = 'yes', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${social_quotient_raw} != null, round(${social_quotient_raw}), null)</t>
+        </is>
+      </c>
+      <c r="K245" t="inlineStr"/>
+      <c r="L245" t="inlineStr"/>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -5082,14 +7204,23 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>total_no_items</t>
-        </is>
-      </c>
+          <t>sq_interpretation</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
       <c r="J246" t="inlineStr">
         <is>
-          <t>if(${item_1} = 'no', 1, 0) + if(${item_2} = 'no', 1, 0) + if(${item_3} = 'no', 1, 0) + if(${item_4} = 'no', 1, 0) + if(${item_5} = 'no', 1, 0) + if(${item_6} = 'no', 1, 0) + if(${item_7} = 'no', 1, 0) + if(${item_8} = 'no', 1, 0) + if(${item_9} = 'no', 1, 0) + if(${item_10} = 'no', 1, 0) + if(${item_11} = 'no', 1, 0) + if(${item_12} = 'no', 1, 0) + if(${item_13} = 'no', 1, 0) + if(${item_14} = 'no', 1, 0) + if(${item_15} = 'no', 1, 0) + if(${item_16} = 'no', 1, 0) + if(${item_17} = 'no', 1, 0) + if(${item_18} = 'no', 1, 0) + if(${item_19} = 'no', 1, 0) + if(${item_20} = 'no', 1, 0) + if(${item_21} = 'no', 1, 0) + if(${item_22} = 'no', 1, 0) + if(${item_23} = 'no', 1, 0) + if(${item_24} = 'no', 1, 0) + if(${item_25} = 'no', 1, 0) + if(${item_26} = 'no', 1, 0) + if(${item_27} = 'no', 1, 0) + if(${item_28} = 'no', 1, 0) + if(${item_29} = 'no', 1, 0) + if(${item_30} = 'no', 1, 0) + if(${item_31} = 'no', 1, 0) + if(${item_32} = 'no', 1, 0) + if(${item_33} = 'no', 1, 0) + if(${item_34} = 'no', 1, 0) + if(${item_35} = 'no', 1, 0) + if(${item_36} = 'no', 1, 0) + if(${item_37} = 'no', 1, 0) + if(${item_38} = 'no', 1, 0) + if(${item_39} = 'no', 1, 0) + if(${item_40} = 'no', 1, 0) + if(${item_41} = 'no', 1, 0) + if(${item_42} = 'no', 1, 0) + if(${item_43} = 'no', 1, 0) + if(${item_44} = 'no', 1, 0) + if(${item_45} = 'no', 1, 0) + if(${item_46} = 'no', 1, 0) + if(${item_47} = 'no', 1, 0) + if(${item_48} = 'no', 1, 0) + if(${item_49} = 'no', 1, 0) + if(${item_50} = 'no', 1, 0) + if(${item_51} = 'no', 1, 0) + if(${item_52} = 'no', 1, 0) + if(${item_53} = 'no', 1, 0) + if(${item_54} = 'no', 1, 0) + if(${item_55} = 'no', 1, 0) + if(${item_56} = 'no', 1, 0) + if(${item_57} = 'no', 1, 0) + if(${item_58} = 'no', 1, 0) + if(${item_59} = 'no', 1, 0) + if(${item_60} = 'no', 1, 0) + if(${item_61} = 'no', 1, 0) + if(${item_62} = 'no', 1, 0) + if(${item_63} = 'no', 1, 0) + if(${item_64} = 'no', 1, 0) + if(${item_65} = 'no', 1, 0) + if(${item_66} = 'no', 1, 0) + if(${item_67} = 'no', 1, 0) + if(${item_68} = 'no', 1, 0) + if(${item_69} = 'no', 1, 0) + if(${item_70} = 'no', 1, 0) + if(${item_71} = 'no', 1, 0) + if(${item_72} = 'no', 1, 0) + if(${item_73} = 'no', 1, 0) + if(${item_74} = 'no', 1, 0) + if(${item_75} = 'no', 1, 0) + if(${item_76} = 'no', 1, 0) + if(${item_77} = 'no', 1, 0) + if(${item_78} = 'no', 1, 0) + if(${item_79} = 'no', 1, 0) + if(${item_80} = 'no', 1, 0) + if(${item_81} = 'no', 1, 0) + if(${item_82} = 'no', 1, 0) + if(${item_83} = 'no', 1, 0) + if(${item_84} = 'no', 1, 0) + if(${item_85} = 'no', 1, 0) + if(${item_86} = 'no', 1, 0) + if(${item_87} = 'no', 1, 0) + if(${item_88} = 'no', 1, 0) + if(${item_89} = 'no', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${social_quotient_rounded} == null, 'Not interpretable (age = 0)', if(${score_status} != 'complete', 'Incomplete', if(${social_quotient_rounded} &gt;= 130, 'Very Superior (Markedly Advanced)', if(${social_quotient_rounded} &gt;= 120, 'Superior', if(${social_quotient_rounded} &gt;= 110, 'High Average', if(${social_quotient_rounded} &gt;= 90, 'Average', if(${social_quotient_rounded} &gt;= 80, 'Low Average', if(${social_quotient_rounded} &gt;= 70, 'Borderline', 'Social Developmental Delay'))))))))</t>
+        </is>
+      </c>
+      <c r="K246" t="inlineStr"/>
+      <c r="L246" t="inlineStr"/>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -5099,158 +7230,265 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>total_not_assessed_items</t>
-        </is>
-      </c>
+          <t>score_status</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr"/>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr"/>
+      <c r="H247" t="inlineStr"/>
+      <c r="I247" t="inlineStr"/>
       <c r="J247" t="inlineStr">
         <is>
-          <t>if(${item_1} = 'not_assessed', 1, 0) + if(${item_2} = 'not_assessed', 1, 0) + if(${item_3} = 'not_assessed', 1, 0) + if(${item_4} = 'not_assessed', 1, 0) + if(${item_5} = 'not_assessed', 1, 0) + if(${item_6} = 'not_assessed', 1, 0) + if(${item_7} = 'not_assessed', 1, 0) + if(${item_8} = 'not_assessed', 1, 0) + if(${item_9} = 'not_assessed', 1, 0) + if(${item_10} = 'not_assessed', 1, 0) + if(${item_11} = 'not_assessed', 1, 0) + if(${item_12} = 'not_assessed', 1, 0) + if(${item_13} = 'not_assessed', 1, 0) + if(${item_14} = 'not_assessed', 1, 0) + if(${item_15} = 'not_assessed', 1, 0) + if(${item_16} = 'not_assessed', 1, 0) + if(${item_17} = 'not_assessed', 1, 0) + if(${item_18} = 'not_assessed', 1, 0) + if(${item_19} = 'not_assessed', 1, 0) + if(${item_20} = 'not_assessed', 1, 0) + if(${item_21} = 'not_assessed', 1, 0) + if(${item_22} = 'not_assessed', 1, 0) + if(${item_23} = 'not_assessed', 1, 0) + if(${item_24} = 'not_assessed', 1, 0) + if(${item_25} = 'not_assessed', 1, 0) + if(${item_26} = 'not_assessed', 1, 0) + if(${item_27} = 'not_assessed', 1, 0) + if(${item_28} = 'not_assessed', 1, 0) + if(${item_29} = 'not_assessed', 1, 0) + if(${item_30} = 'not_assessed', 1, 0) + if(${item_31} = 'not_assessed', 1, 0) + if(${item_32} = 'not_assessed', 1, 0) + if(${item_33} = 'not_assessed', 1, 0) + if(${item_34} = 'not_assessed', 1, 0) + if(${item_35} = 'not_assessed', 1, 0) + if(${item_36} = 'not_assessed', 1, 0) + if(${item_37} = 'not_assessed', 1, 0) + if(${item_38} = 'not_assessed', 1, 0) + if(${item_39} = 'not_assessed', 1, 0) + if(${item_40} = 'not_assessed', 1, 0) + if(${item_41} = 'not_assessed', 1, 0) + if(${item_42} = 'not_assessed', 1, 0) + if(${item_43} = 'not_assessed', 1, 0) + if(${item_44} = 'not_assessed', 1, 0) + if(${item_45} = 'not_assessed', 1, 0) + if(${item_46} = 'not_assessed', 1, 0) + if(${item_47} = 'not_assessed', 1, 0) + if(${item_48} = 'not_assessed', 1, 0) + if(${item_49} = 'not_assessed', 1, 0) + if(${item_50} = 'not_assessed', 1, 0) + if(${item_51} = 'not_assessed', 1, 0) + if(${item_52} = 'not_assessed', 1, 0) + if(${item_53} = 'not_assessed', 1, 0) + if(${item_54} = 'not_assessed', 1, 0) + if(${item_55} = 'not_assessed', 1, 0) + if(${item_56} = 'not_assessed', 1, 0) + if(${item_57} = 'not_assessed', 1, 0) + if(${item_58} = 'not_assessed', 1, 0) + if(${item_59} = 'not_assessed', 1, 0) + if(${item_60} = 'not_assessed', 1, 0) + if(${item_61} = 'not_assessed', 1, 0) + if(${item_62} = 'not_assessed', 1, 0) + if(${item_63} = 'not_assessed', 1, 0) + if(${item_64} = 'not_assessed', 1, 0) + if(${item_65} = 'not_assessed', 1, 0) + if(${item_66} = 'not_assessed', 1, 0) + if(${item_67} = 'not_assessed', 1, 0) + if(${item_68} = 'not_assessed', 1, 0) + if(${item_69} = 'not_assessed', 1, 0) + if(${item_70} = 'not_assessed', 1, 0) + if(${item_71} = 'not_assessed', 1, 0) + if(${item_72} = 'not_assessed', 1, 0) + if(${item_73} = 'not_assessed', 1, 0) + if(${item_74} = 'not_assessed', 1, 0) + if(${item_75} = 'not_assessed', 1, 0) + if(${item_76} = 'not_assessed', 1, 0) + if(${item_77} = 'not_assessed', 1, 0) + if(${item_78} = 'not_assessed', 1, 0) + if(${item_79} = 'not_assessed', 1, 0) + if(${item_80} = 'not_assessed', 1, 0) + if(${item_81} = 'not_assessed', 1, 0) + if(${item_82} = 'not_assessed', 1, 0) + if(${item_83} = 'not_assessed', 1, 0) + if(${item_84} = 'not_assessed', 1, 0) + if(${item_85} = 'not_assessed', 1, 0) + if(${item_86} = 'not_assessed', 1, 0) + if(${item_87} = 'not_assessed', 1, 0) + if(${item_88} = 'not_assessed', 1, 0) + if(${item_89} = 'not_assessed', 1, 0)</t>
-        </is>
-      </c>
+          <t>if(${age_valid} != 'yes', 'invalid_age', if(${total_not_assessed_items} &gt; 0, 'incomplete', 'complete'))</t>
+        </is>
+      </c>
+      <c r="K247" t="inlineStr"/>
+      <c r="L247" t="inlineStr"/>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>social_age_months</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>if(${raw_score} = 0, 0, if(${raw_score} = 1, 1, if(${raw_score} = 2, 2, if(${raw_score} = 3, 3, if(${raw_score} = 4, 4, if(${raw_score} = 5, 5, if(${raw_score} = 6, 6, if(${raw_score} = 7, 7, if(${raw_score} = 8, 8, if(${raw_score} = 9, 9, if(${raw_score} = 10, 10, if(${raw_score} = 11, 11, if(${raw_score} = 12, 12, if(${raw_score} = 13, 13, if(${raw_score} = 14, 14, if(${raw_score} = 15, 15, if(${raw_score} = 16, 16, if(${raw_score} = 17, 17, if(${raw_score} = 18, 18, if(${raw_score} = 19, 19, if(${raw_score} = 20, 20, if(${raw_score} = 21, 21, if(${raw_score} = 22, 22, if(${raw_score} = 23, 23, if(${raw_score} = 24, 24, if(${raw_score} = 25, 25, if(${raw_score} = 26, 26, if(${raw_score} = 27, 27, if(${raw_score} = 28, 28, if(${raw_score} = 29, 29, if(${raw_score} = 30, 30, if(${raw_score} = 31, 31, if(${raw_score} = 32, 32, if(${raw_score} = 33, 33, if(${raw_score} = 34, 34, if(${raw_score} = 35, 35, if(${raw_score} = 36, 36, if(${raw_score} = 37, 37, if(${raw_score} = 38, 38, if(${raw_score} = 39, 39, if(${raw_score} = 40, 40, if(${raw_score} = 41, 41, if(${raw_score} = 42, 42, if(${raw_score} = 43, 43, if(${raw_score} = 44, 44, if(${raw_score} = 45, 45, if(${raw_score} = 46, 46, if(${raw_score} = 47, 47, if(${raw_score} = 48, 48, if(${raw_score} = 49, 49, if(${raw_score} = 50, 50, if(${raw_score} = 51, 51, if(${raw_score} = 52, 52, if(${raw_score} = 53, 53, if(${raw_score} = 54, 54, if(${raw_score} = 55, 55, if(${raw_score} = 56, 56, if(${raw_score} = 57, 57, if(${raw_score} = 58, 58, if(${raw_score} = 59, 59, if(${raw_score} = 60, 60, if(${raw_score} = 61, 61, if(${raw_score} = 62, 62, if(${raw_score} = 63, 63, if(${raw_score} = 64, 64, if(${raw_score} = 65, 65, if(${raw_score} = 66, 66, if(${raw_score} = 67, 67, if(${raw_score} = 68, 68, if(${raw_score} = 69, 69, if(${raw_score} = 70, 70, if(${raw_score} = 71, 71, if(${raw_score} = 72, 72, if(${raw_score} = 73, 73, if(${raw_score} = 74, 74, if(${raw_score} = 75, 75, if(${raw_score} = 76, 76, if(${raw_score} = 77, 77, if(${raw_score} = 78, 78, if(${raw_score} = 79, 79, if(${raw_score} = 80, 80, if(${raw_score} = 81, 81, if(${raw_score} = 82, 82, if(${raw_score} = 83, 83, if(${raw_score} = 84, 84, if(${raw_score} = 85, 85, if(${raw_score} = 86, 86, if(${raw_score} = 87, 87, if(${raw_score} = 88, 88, if(${raw_score} = 89, 89, 0))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))))</t>
-        </is>
-      </c>
+          <t>na_reason</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Reason for items not assessed</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t>true()</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>${total_not_assessed_items} &gt; 0</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
+      <c r="K248" t="inlineStr"/>
+      <c r="L248" t="inlineStr"/>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>social_age_years</t>
-        </is>
-      </c>
-      <c r="J249" t="inlineStr">
-        <is>
-          <t>floor(${social_age_months} div 12)</t>
-        </is>
-      </c>
+          <t>clinical_notes</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Clinical notes</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr"/>
+      <c r="H249" t="inlineStr"/>
+      <c r="I249" t="inlineStr"/>
+      <c r="J249" t="inlineStr"/>
+      <c r="K249" t="inlineStr"/>
+      <c r="L249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>social_age_remaining_months</t>
-        </is>
-      </c>
-      <c r="J250" t="inlineStr">
-        <is>
-          <t>${social_age_months} - (${social_age_years} * 12)</t>
-        </is>
-      </c>
+          <t>result_complete</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>✅ Assessment complete. Social Quotient: ${social_quotient_rounded} (${sq_interpretation}).</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>${score_status} = 'complete'</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr"/>
+      <c r="I250" t="inlineStr"/>
+      <c r="J250" t="inlineStr"/>
+      <c r="K250" t="inlineStr"/>
+      <c r="L250" t="inlineStr"/>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>social_quotient_raw</t>
-        </is>
-      </c>
-      <c r="J251" t="inlineStr">
-        <is>
-          <t>if(${age_valid} = 'yes' and ${ca_months_dec} &gt; 0, ${social_age_months} div ${ca_months_dec} * 100, '')</t>
-        </is>
-      </c>
+          <t>result_incomplete</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>⚠️ Score incomplete — clinician review required. Some items were not assessed.</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>${score_status} = 'incomplete'</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr"/>
+      <c r="I251" t="inlineStr"/>
+      <c r="J251" t="inlineStr"/>
+      <c r="K251" t="inlineStr"/>
+      <c r="L251" t="inlineStr"/>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>social_quotient_rounded</t>
-        </is>
-      </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>if(${social_quotient_raw} != '', round(${social_quotient_raw}), '')</t>
-        </is>
-      </c>
+          <t>result_invalid</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>❌ Invalid age: child must be 0–15 years for VSMS.</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>${score_status} = 'invalid_age'}</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr"/>
+      <c r="L252" t="inlineStr"/>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin group</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>sq_interpretation</t>
-        </is>
-      </c>
-      <c r="J253" t="inlineStr">
-        <is>
-          <t>if(${score_status} != 'complete', 'Incomplete', if(${social_quotient_rounded} &gt;= 90, 'Average', if(${social_quotient_rounded} &gt;= 80, 'Low Average', if(${social_quotient_rounded} &gt;= 70, 'Borderline', 'Social Developmental Delay'))))</t>
-        </is>
-      </c>
+          <t>g_supporting_docs</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Supporting Documents / Scale Upload</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr"/>
+      <c r="H253" t="inlineStr"/>
+      <c r="I253" t="inlineStr"/>
+      <c r="J253" t="inlineStr"/>
+      <c r="K253" t="inlineStr"/>
+      <c r="L253" t="inlineStr"/>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>image</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>score_status</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>if(${age_valid} != 'yes', 'invalid_age', if(${total_not_assessed_items} &gt; 0, 'incomplete', 'complete'))</t>
+          <t>upload_scale_image</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Upload completed scale / assessment sheet (image)</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Upload clear photos of the completed paper scale, consent form, or supporting assessment document. Accepts JPG, JPEG, PNG. For PDF use next field.</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
+      <c r="K254" t="inlineStr"/>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>binary</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>file</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>na_reason</t>
+          <t>upload_scale_pdf</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Reason for items not assessed</t>
-        </is>
-      </c>
-      <c r="E255" t="inlineStr">
-        <is>
-          <t>true()</t>
-        </is>
-      </c>
-      <c r="G255" t="inlineStr">
-        <is>
-          <t>${total_not_assessed_items} &gt; 0</t>
+          <t>Upload completed scale / assessment sheet (PDF)</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>Upload a PDF of the completed paper scale if not already uploaded as image. Accepts PDF.</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr"/>
+      <c r="H255" t="inlineStr"/>
+      <c r="I255" t="inlineStr"/>
+      <c r="J255" t="inlineStr"/>
+      <c r="K255" t="inlineStr"/>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>binary</t>
         </is>
       </c>
     </row>
@@ -5262,209 +7500,93 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>clinical_notes</t>
+          <t>upload_caption</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Clinical notes</t>
-        </is>
-      </c>
+          <t>Attachment caption / description (optional)</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr"/>
+      <c r="H256" t="inlineStr"/>
+      <c r="I256" t="inlineStr"/>
+      <c r="J256" t="inlineStr"/>
+      <c r="K256" t="inlineStr"/>
+      <c r="L256" t="inlineStr"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B257" t="inlineStr">
-        <is>
-          <t>result_complete</t>
-        </is>
-      </c>
-      <c r="C257" t="inlineStr">
-        <is>
-          <t>✅ Assessment complete. Social Quotient: ${social_quotient_rounded} (${sq_interpretation}).</t>
-        </is>
-      </c>
-      <c r="G257" t="inlineStr">
-        <is>
-          <t>${score_status} = 'complete'</t>
-        </is>
-      </c>
+          <t>end group</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr"/>
+      <c r="C257" t="inlineStr"/>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr"/>
+      <c r="H257" t="inlineStr"/>
+      <c r="I257" t="inlineStr"/>
+      <c r="J257" t="inlineStr"/>
+      <c r="K257" t="inlineStr"/>
+      <c r="L257" t="inlineStr"/>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>result_incomplete</t>
-        </is>
-      </c>
-      <c r="C258" t="inlineStr">
-        <is>
-          <t>⚠️ Score incomplete — clinician review required. Some items were not assessed.</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>${score_status} = 'incomplete'</t>
-        </is>
-      </c>
+          <t>scoring_version</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr"/>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr"/>
+      <c r="H258" t="inlineStr"/>
+      <c r="I258" t="inlineStr"/>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>'vsms-v1-doll1965-1to1'</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr"/>
+      <c r="L258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>result_invalid</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>❌ Invalid age: child must be 0–15 years for VSMS.</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>${score_status} = 'invalid_age'</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr">
-        <is>
-          <t>begin group</t>
-        </is>
-      </c>
-      <c r="B260" t="inlineStr">
-        <is>
-          <t>g_supporting_docs</t>
-        </is>
-      </c>
-      <c r="C260" t="inlineStr">
-        <is>
-          <t>Supporting Documents / Scale Upload</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr">
-        <is>
-          <t>image</t>
-        </is>
-      </c>
-      <c r="B261" t="inlineStr">
-        <is>
-          <t>upload_scale_image</t>
-        </is>
-      </c>
-      <c r="C261" t="inlineStr">
-        <is>
-          <t>Upload completed scale / assessment sheet (image)</t>
-        </is>
-      </c>
-      <c r="D261" t="inlineStr">
-        <is>
-          <t>Upload clear photos of the completed paper scale, consent form, or supporting assessment document. Accepts JPG, JPEG, PNG. For PDF use next field.</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>file</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>upload_scale_pdf</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>Upload completed scale / assessment sheet (PDF)</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>Upload a PDF of the completed paper scale if not already uploaded as image. Accepts PDF.</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>binary</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B263" t="inlineStr">
-        <is>
-          <t>upload_caption</t>
-        </is>
-      </c>
-      <c r="C263" t="inlineStr">
-        <is>
-          <t>Attachment caption / description (optional)</t>
-        </is>
-      </c>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr">
-        <is>
-          <t>end group</t>
-        </is>
-      </c>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>scoring_version</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>'vsms-v1-doll1965-1to1'</t>
-        </is>
-      </c>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr">
-        <is>
-          <t>calculate</t>
-        </is>
-      </c>
-      <c r="B266" t="inlineStr">
-        <is>
           <t>scoring_notes</t>
         </is>
       </c>
-      <c r="J266" t="inlineStr">
+      <c r="C259" t="inlineStr"/>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr"/>
+      <c r="H259" t="inlineStr"/>
+      <c r="I259" t="inlineStr"/>
+      <c r="J259" t="inlineStr">
         <is>
           <t>'Doll 1965 VSMS 1:1 raw=SA months (0-89). SQ=SA/CA*100. Internet snippet (40-&gt;54,42-&gt;60,45-&gt;66) differs from manual.'</t>
         </is>
       </c>
+      <c r="K259" t="inlineStr"/>
+      <c r="L259" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
